--- a/data/Features description LendingClub.xlsx
+++ b/data/Features description LendingClub.xlsx
@@ -5,10 +5,10 @@
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oskarklima/Documents/Oskar/Škola/Bakalářka/Praktická část/Final data Lending Club/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oskarklima/Documents/Oskar/Škola/Bakalářka/Praktická část/Github/bachelor_thesis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD70BC08-62EA-0446-9F3F-6F1E797D813C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF9879F3-8987-BD46-A44D-3315644469AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="631">
   <si>
     <t>id</t>
   </si>
@@ -1736,9 +1736,6 @@
     <t>Odstraněno (text a duplicita s proměnnou purpose)</t>
   </si>
   <si>
-    <t>Dropped (tect and duplicate of purpose variable)</t>
-  </si>
-  <si>
     <t>Odstarněno (939 kategorií a odpovídá addr_state)</t>
   </si>
   <si>
@@ -1751,12 +1748,6 @@
     <t>Used (continuous variable) - converted to average</t>
   </si>
   <si>
-    <t>publicly available policy_code=1</t>
-  </si>
-  <si>
-    <t>new products not publicly available policy_code=2</t>
-  </si>
-  <si>
     <t>Odstraněno (konstantní hodnota)</t>
   </si>
   <si>
@@ -1847,15 +1838,6 @@
     <t>Average of fico_range_low and fico_range_high</t>
   </si>
   <si>
-    <t>issue_d_year</t>
-  </si>
-  <si>
-    <t>Rok issue_d</t>
-  </si>
-  <si>
-    <t>Year extracted from issue_d</t>
-  </si>
-  <si>
     <t>issue_d_month</t>
   </si>
   <si>
@@ -1892,15 +1874,6 @@
     <t>Credit history length from earliest_cr_line to issue_d in months</t>
   </si>
   <si>
-    <t>issue_d_numeric</t>
-  </si>
-  <si>
-    <t>Délka od 1.1.1970 do issue_d ve dnech</t>
-  </si>
-  <si>
-    <t>Number of days from January 1, 1970, to issue_d</t>
-  </si>
-  <si>
     <t>earliest_cr_line_numeric</t>
   </si>
   <si>
@@ -1956,6 +1929,15 @@
   </si>
   <si>
     <t>Zdroj - Source: https://github.com/bacover/Capstone-LendingClub/blob/main/LCDataDictionary.xlsx</t>
+  </si>
+  <si>
+    <t>Využito/Used</t>
+  </si>
+  <si>
+    <t>publicly available policy_code=1, new products not publicly available policy_code=2</t>
+  </si>
+  <si>
+    <t>Dropped (text and duplicate of purpose variable)</t>
   </si>
 </sst>
 </file>
@@ -2556,7 +2538,13 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
   </cellXfs>
   <cellStyles count="54">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2614,10 +2602,10 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="14">
     <dxf>
       <font>
-        <b/>
+        <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -2741,6 +2729,132 @@
         <scheme val="minor"/>
       </font>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2754,15 +2868,33 @@
 </styleSheet>
 </file>
 
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EE29E4E4-43B3-174E-8F3B-5AB70E293FBE}" name="Table2" displayName="Table2" ref="A3:E171" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
-  <autoFilter ref="A3:E171" xr:uid="{EE29E4E4-43B3-174E-8F3B-5AB70E293FBE}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{F3E53C65-DD0F-CB46-8219-E6650EF65E70}" name="Sloupec" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{3A02C682-E8DB-384F-9ED3-84A3FF96F6A6}" name="Český popis" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{5042C38D-E653-3547-BE39-3134ABFE15C8}" name="Anglický popis" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{004D6F80-4F83-9F4D-BBA3-AD6ACAAE4B8F}" name="Zpracování" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{FC8D4EE5-BDDE-1F42-89F2-9A6E869944FE}" name="Processing" dataDxfId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EE29E4E4-43B3-174E-8F3B-5AB70E293FBE}" name="Table2" displayName="Table2" ref="A3:F168" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="A3:F168" xr:uid="{EE29E4E4-43B3-174E-8F3B-5AB70E293FBE}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{F3E53C65-DD0F-CB46-8219-E6650EF65E70}" name="Sloupec" dataDxfId="11" totalsRowDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{3A02C682-E8DB-384F-9ED3-84A3FF96F6A6}" name="Český popis" dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{5042C38D-E653-3547-BE39-3134ABFE15C8}" name="Anglický popis" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{004D6F80-4F83-9F4D-BBA3-AD6ACAAE4B8F}" name="Zpracování" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{FC8D4EE5-BDDE-1F42-89F2-9A6E869944FE}" name="Processing" dataDxfId="3" totalsRowDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{E8212FED-A26F-EB4D-B375-A7BBE53E82D6}" name="Využito/Used" dataDxfId="1" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3055,7 +3187,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3238AAFA-B3F0-564C-8C8D-8D5C3EA0B867}">
-  <dimension ref="A1:H171"/>
+  <dimension ref="A1:G168"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.1640625" bestFit="1" customWidth="1"/>
@@ -3063,24 +3195,21 @@
     <col min="3" max="3" width="179" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="67.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="60.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="57" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="F1" s="12"/>
       <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="F2" s="12"/>
       <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-    </row>
-    <row r="3" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
         <v>369</v>
       </c>
@@ -3096,3236 +3225,3368 @@
       <c r="E3" s="11" t="s">
         <v>524</v>
       </c>
-      <c r="F3" s="12"/>
+      <c r="F3" s="11" t="s">
+        <v>628</v>
+      </c>
       <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="14" t="s">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" t="s">
         <v>373</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" t="s">
         <v>539</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" t="s">
         <v>540</v>
       </c>
-      <c r="F4" s="12"/>
+      <c r="F4" s="14" t="b">
+        <v>0</v>
+      </c>
       <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="14" t="s">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
         <v>374</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" t="s">
         <v>72</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" t="s">
         <v>541</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" t="s">
         <v>542</v>
       </c>
-      <c r="F5" s="12"/>
+      <c r="F5" s="14" t="b">
+        <v>0</v>
+      </c>
       <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="14" t="s">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" t="s">
         <v>375</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" t="s">
         <v>525</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" t="s">
         <v>526</v>
       </c>
-      <c r="F6" s="12"/>
+      <c r="F6" s="14" t="b">
+        <v>1</v>
+      </c>
       <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="14" t="s">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" t="s">
         <v>376</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" t="s">
         <v>227</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" t="s">
         <v>543</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" t="s">
         <v>544</v>
       </c>
-      <c r="F7" s="12"/>
+      <c r="F7" s="14" t="b">
+        <v>0</v>
+      </c>
       <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="14" t="s">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" t="s">
         <v>377</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" t="s">
         <v>228</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" t="s">
         <v>545</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" t="s">
         <v>546</v>
       </c>
-      <c r="F8" s="12"/>
+      <c r="F8" s="14" t="b">
+        <v>0</v>
+      </c>
       <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="14" t="s">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" t="s">
         <v>378</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" t="s">
         <v>547</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" t="s">
         <v>548</v>
       </c>
-      <c r="F9" s="12"/>
+      <c r="F9" s="14" t="b">
+        <v>0</v>
+      </c>
       <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="14" t="s">
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" t="s">
         <v>379</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" t="s">
         <v>525</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" t="s">
         <v>526</v>
       </c>
-      <c r="F10" s="12"/>
+      <c r="F10" s="14" t="b">
+        <v>1</v>
+      </c>
       <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="14" t="s">
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" t="s">
         <v>380</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" t="s">
         <v>69</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" t="s">
         <v>525</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" t="s">
         <v>526</v>
       </c>
-      <c r="F11" s="12"/>
+      <c r="F11" s="14" t="b">
+        <v>1</v>
+      </c>
       <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="14" t="s">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" t="s">
         <v>381</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" t="s">
         <v>549</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" t="s">
         <v>550</v>
       </c>
-      <c r="F12" s="12"/>
+      <c r="F12" s="14" t="b">
+        <v>0</v>
+      </c>
       <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="14" t="s">
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" t="s">
         <v>382</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" t="s">
         <v>85</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" t="s">
         <v>527</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" t="s">
         <v>528</v>
       </c>
-      <c r="F13" s="12"/>
+      <c r="F13" s="14" t="b">
+        <v>1</v>
+      </c>
       <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="14" t="s">
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>173</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" t="s">
         <v>383</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" t="s">
         <v>174</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" t="s">
         <v>529</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" t="s">
         <v>530</v>
       </c>
-      <c r="F14" s="12"/>
+      <c r="F14" s="14" t="b">
+        <v>0</v>
+      </c>
       <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="14" t="s">
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" t="s">
         <v>384</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" t="s">
         <v>185</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" t="s">
         <v>527</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" t="s">
         <v>528</v>
       </c>
-      <c r="F15" s="12"/>
+      <c r="F15" s="14" t="b">
+        <v>1</v>
+      </c>
       <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="14" t="s">
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" t="s">
         <v>385</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" t="s">
         <v>551</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" t="s">
         <v>552</v>
       </c>
-      <c r="F16" s="12"/>
+      <c r="F16" s="14" t="b">
+        <v>1</v>
+      </c>
       <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="14" t="s">
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" t="s">
         <v>386</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" t="s">
         <v>525</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" t="s">
         <v>526</v>
       </c>
-      <c r="F17" s="12"/>
+      <c r="F17" s="14" t="b">
+        <v>1</v>
+      </c>
       <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="14" t="s">
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>259</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" t="s">
         <v>387</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" t="s">
         <v>229</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" t="s">
         <v>531</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" t="s">
         <v>532</v>
       </c>
-      <c r="F18" s="12"/>
+      <c r="F18" s="14" t="b">
+        <v>1</v>
+      </c>
       <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="14" t="s">
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" t="s">
         <v>388</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" t="s">
         <v>255</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" t="s">
         <v>553</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E19" t="s">
         <v>554</v>
       </c>
-      <c r="F19" s="12"/>
+      <c r="F19" s="14" t="b">
+        <v>1</v>
+      </c>
       <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="14" t="s">
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" t="s">
         <v>389</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" t="s">
         <v>95</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" t="s">
         <v>555</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="E20" t="s">
         <v>556</v>
       </c>
-      <c r="F20" s="12"/>
+      <c r="F20" s="14" t="b">
+        <v>0</v>
+      </c>
       <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="14" t="s">
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" t="s">
         <v>390</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" t="s">
         <v>98</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" t="s">
         <v>557</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" t="s">
         <v>558</v>
       </c>
-      <c r="F21" s="12"/>
+      <c r="F21" s="14" t="b">
+        <v>0</v>
+      </c>
       <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="14" t="s">
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" t="s">
         <v>391</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" t="s">
         <v>91</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" t="s">
         <v>533</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E22" t="s">
         <v>534</v>
       </c>
-      <c r="F22" s="12"/>
+      <c r="F22" s="14" t="b">
+        <v>0</v>
+      </c>
       <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="14" t="s">
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" t="s">
         <v>392</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" t="s">
         <v>58</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="D23" t="s">
         <v>559</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" t="s">
         <v>560</v>
       </c>
-      <c r="F23" s="12"/>
+      <c r="F23" s="14" t="b">
+        <v>0</v>
+      </c>
       <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="14" t="s">
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" t="s">
         <v>393</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" t="s">
         <v>561</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="D24" t="s">
         <v>531</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="E24" t="s">
         <v>532</v>
       </c>
-      <c r="F24" s="12"/>
+      <c r="F24" s="14" t="b">
+        <v>1</v>
+      </c>
       <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="14" t="s">
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
         <v>20</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" t="s">
         <v>394</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C25" t="s">
         <v>87</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="D25" t="s">
         <v>562</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="E25" t="s">
+        <v>630</v>
+      </c>
+      <c r="F25" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="13"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>254</v>
+      </c>
+      <c r="B26" t="s">
+        <v>395</v>
+      </c>
+      <c r="C26" t="s">
+        <v>253</v>
+      </c>
+      <c r="D26" t="s">
         <v>563</v>
       </c>
-      <c r="F25" s="12"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>395</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="D26" s="14" t="s">
+      <c r="E26" t="s">
         <v>564</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="F26" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="13"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" t="s">
+        <v>396</v>
+      </c>
+      <c r="C27" t="s">
+        <v>248</v>
+      </c>
+      <c r="D27" t="s">
+        <v>531</v>
+      </c>
+      <c r="E27" t="s">
+        <v>532</v>
+      </c>
+      <c r="F27" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G27" s="13"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" t="s">
+        <v>397</v>
+      </c>
+      <c r="C28" t="s">
+        <v>249</v>
+      </c>
+      <c r="D28" t="s">
+        <v>525</v>
+      </c>
+      <c r="E28" t="s">
+        <v>526</v>
+      </c>
+      <c r="F28" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="13"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" t="s">
+        <v>398</v>
+      </c>
+      <c r="C29" t="s">
+        <v>56</v>
+      </c>
+      <c r="D29" t="s">
+        <v>525</v>
+      </c>
+      <c r="E29" t="s">
+        <v>526</v>
+      </c>
+      <c r="F29" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="13"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" t="s">
+        <v>399</v>
+      </c>
+      <c r="C30" t="s">
+        <v>256</v>
+      </c>
+      <c r="D30" t="s">
+        <v>535</v>
+      </c>
+      <c r="E30" t="s">
+        <v>536</v>
+      </c>
+      <c r="F30" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="13"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" t="s">
+        <v>400</v>
+      </c>
+      <c r="C31" t="s">
+        <v>63</v>
+      </c>
+      <c r="D31" t="s">
         <v>565</v>
       </c>
-      <c r="F26" s="12"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>396</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="D27" s="14" t="s">
+      <c r="E31" t="s">
+        <v>566</v>
+      </c>
+      <c r="F31" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G31" s="13"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" t="s">
+        <v>401</v>
+      </c>
+      <c r="C32" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" t="s">
+        <v>565</v>
+      </c>
+      <c r="E32" t="s">
+        <v>566</v>
+      </c>
+      <c r="F32" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G32" s="13"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>27</v>
+      </c>
+      <c r="B33" t="s">
+        <v>402</v>
+      </c>
+      <c r="C33" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" t="s">
+        <v>525</v>
+      </c>
+      <c r="E33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F33" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="13"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34" t="s">
+        <v>403</v>
+      </c>
+      <c r="C34" t="s">
+        <v>74</v>
+      </c>
+      <c r="D34" t="s">
+        <v>525</v>
+      </c>
+      <c r="E34" t="s">
+        <v>526</v>
+      </c>
+      <c r="F34" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" s="13"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" t="s">
+        <v>404</v>
+      </c>
+      <c r="C35" t="s">
+        <v>75</v>
+      </c>
+      <c r="D35" t="s">
+        <v>525</v>
+      </c>
+      <c r="E35" t="s">
+        <v>526</v>
+      </c>
+      <c r="F35" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" s="13"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" t="s">
+        <v>405</v>
+      </c>
+      <c r="C36" t="s">
+        <v>80</v>
+      </c>
+      <c r="D36" t="s">
+        <v>525</v>
+      </c>
+      <c r="E36" t="s">
+        <v>526</v>
+      </c>
+      <c r="F36" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" s="13"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>31</v>
+      </c>
+      <c r="B37" t="s">
+        <v>406</v>
+      </c>
+      <c r="C37" t="s">
+        <v>82</v>
+      </c>
+      <c r="D37" t="s">
+        <v>525</v>
+      </c>
+      <c r="E37" t="s">
+        <v>526</v>
+      </c>
+      <c r="F37" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" s="13"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>32</v>
+      </c>
+      <c r="B38" t="s">
+        <v>407</v>
+      </c>
+      <c r="C38" t="s">
+        <v>83</v>
+      </c>
+      <c r="D38" t="s">
+        <v>525</v>
+      </c>
+      <c r="E38" t="s">
+        <v>526</v>
+      </c>
+      <c r="F38" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" s="13"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>33</v>
+      </c>
+      <c r="B39" t="s">
+        <v>408</v>
+      </c>
+      <c r="C39" t="s">
+        <v>84</v>
+      </c>
+      <c r="D39" t="s">
+        <v>525</v>
+      </c>
+      <c r="E39" t="s">
+        <v>526</v>
+      </c>
+      <c r="F39" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" s="13"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>34</v>
+      </c>
+      <c r="B40" t="s">
+        <v>409</v>
+      </c>
+      <c r="C40" t="s">
+        <v>88</v>
+      </c>
+      <c r="D40" t="s">
+        <v>525</v>
+      </c>
+      <c r="E40" t="s">
+        <v>526</v>
+      </c>
+      <c r="F40" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" s="13"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41" t="s">
+        <v>410</v>
+      </c>
+      <c r="C41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D41" t="s">
         <v>531</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="E41" t="s">
         <v>532</v>
       </c>
-      <c r="F27" s="12"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>397</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="D28" s="14" t="s">
+      <c r="F41" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" s="13"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>36</v>
+      </c>
+      <c r="B42" t="s">
+        <v>411</v>
+      </c>
+      <c r="C42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D42" t="s">
+        <v>537</v>
+      </c>
+      <c r="E42" t="s">
+        <v>538</v>
+      </c>
+      <c r="F42" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G42" s="13"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" t="s">
+        <v>412</v>
+      </c>
+      <c r="C43" t="s">
+        <v>97</v>
+      </c>
+      <c r="D43" t="s">
+        <v>537</v>
+      </c>
+      <c r="E43" t="s">
+        <v>538</v>
+      </c>
+      <c r="F43" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G43" s="13"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" t="s">
+        <v>413</v>
+      </c>
+      <c r="C44" t="s">
+        <v>99</v>
+      </c>
+      <c r="D44" t="s">
+        <v>537</v>
+      </c>
+      <c r="E44" t="s">
+        <v>538</v>
+      </c>
+      <c r="F44" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G44" s="13"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" t="s">
+        <v>414</v>
+      </c>
+      <c r="C45" t="s">
+        <v>100</v>
+      </c>
+      <c r="D45" t="s">
+        <v>537</v>
+      </c>
+      <c r="E45" t="s">
+        <v>538</v>
+      </c>
+      <c r="F45" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G45" s="13"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" t="s">
+        <v>415</v>
+      </c>
+      <c r="C46" t="s">
+        <v>103</v>
+      </c>
+      <c r="D46" t="s">
+        <v>537</v>
+      </c>
+      <c r="E46" t="s">
+        <v>538</v>
+      </c>
+      <c r="F46" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G46" s="13"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" t="s">
+        <v>416</v>
+      </c>
+      <c r="C47" t="s">
+        <v>102</v>
+      </c>
+      <c r="D47" t="s">
+        <v>537</v>
+      </c>
+      <c r="E47" t="s">
+        <v>538</v>
+      </c>
+      <c r="F47" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G47" s="13"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" t="s">
+        <v>417</v>
+      </c>
+      <c r="C48" t="s">
+        <v>101</v>
+      </c>
+      <c r="D48" t="s">
+        <v>537</v>
+      </c>
+      <c r="E48" t="s">
+        <v>538</v>
+      </c>
+      <c r="F48" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G48" s="13"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>232</v>
+      </c>
+      <c r="B49" t="s">
+        <v>418</v>
+      </c>
+      <c r="C49" t="s">
+        <v>230</v>
+      </c>
+      <c r="D49" t="s">
+        <v>537</v>
+      </c>
+      <c r="E49" t="s">
+        <v>538</v>
+      </c>
+      <c r="F49" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G49" s="13"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>233</v>
+      </c>
+      <c r="B50" t="s">
+        <v>419</v>
+      </c>
+      <c r="C50" t="s">
+        <v>231</v>
+      </c>
+      <c r="D50" t="s">
+        <v>537</v>
+      </c>
+      <c r="E50" t="s">
+        <v>538</v>
+      </c>
+      <c r="F50" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G50" s="13"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>43</v>
+      </c>
+      <c r="B51" t="s">
+        <v>420</v>
+      </c>
+      <c r="C51" t="s">
+        <v>257</v>
+      </c>
+      <c r="D51" t="s">
+        <v>537</v>
+      </c>
+      <c r="E51" t="s">
+        <v>538</v>
+      </c>
+      <c r="F51" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G51" s="13"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>44</v>
+      </c>
+      <c r="B52" t="s">
+        <v>421</v>
+      </c>
+      <c r="C52" t="s">
+        <v>104</v>
+      </c>
+      <c r="D52" t="s">
+        <v>537</v>
+      </c>
+      <c r="E52" t="s">
+        <v>538</v>
+      </c>
+      <c r="F52" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G52" s="13"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>45</v>
+      </c>
+      <c r="B53" t="s">
+        <v>422</v>
+      </c>
+      <c r="C53" t="s">
+        <v>105</v>
+      </c>
+      <c r="D53" t="s">
+        <v>537</v>
+      </c>
+      <c r="E53" t="s">
+        <v>538</v>
+      </c>
+      <c r="F53" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G53" s="13"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>46</v>
+      </c>
+      <c r="B54" t="s">
+        <v>423</v>
+      </c>
+      <c r="C54" t="s">
+        <v>258</v>
+      </c>
+      <c r="D54" t="s">
+        <v>537</v>
+      </c>
+      <c r="E54" t="s">
+        <v>538</v>
+      </c>
+      <c r="F54" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" s="13"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>47</v>
+      </c>
+      <c r="B55" t="s">
+        <v>424</v>
+      </c>
+      <c r="C55" t="s">
+        <v>93</v>
+      </c>
+      <c r="D55" t="s">
+        <v>537</v>
+      </c>
+      <c r="E55" t="s">
+        <v>538</v>
+      </c>
+      <c r="F55" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G55" s="13"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>48</v>
+      </c>
+      <c r="B56" t="s">
+        <v>425</v>
+      </c>
+      <c r="C56" t="s">
+        <v>94</v>
+      </c>
+      <c r="D56" t="s">
+        <v>537</v>
+      </c>
+      <c r="E56" t="s">
+        <v>538</v>
+      </c>
+      <c r="F56" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G56" s="13"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>113</v>
+      </c>
+      <c r="B57" t="s">
+        <v>426</v>
+      </c>
+      <c r="C57" t="s">
+        <v>138</v>
+      </c>
+      <c r="D57" t="s">
         <v>525</v>
       </c>
-      <c r="E28" s="14" t="s">
+      <c r="E57" t="s">
         <v>526</v>
       </c>
-      <c r="F28" s="12"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>398</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D29" s="14" t="s">
+      <c r="F57" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G57" s="13"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>115</v>
+      </c>
+      <c r="B58" t="s">
+        <v>427</v>
+      </c>
+      <c r="C58" t="s">
+        <v>143</v>
+      </c>
+      <c r="D58" t="s">
         <v>525</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="E58" t="s">
         <v>526</v>
       </c>
-      <c r="F29" s="12"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>399</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>536</v>
-      </c>
-      <c r="F30" s="12"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="14" t="s">
-        <v>400</v>
-      </c>
-      <c r="C31" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>566</v>
-      </c>
-      <c r="E31" s="14" t="s">
+      <c r="F58" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G58" s="13"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>136</v>
+      </c>
+      <c r="B59" t="s">
+        <v>428</v>
+      </c>
+      <c r="C59" t="s">
+        <v>629</v>
+      </c>
+      <c r="D59" t="s">
         <v>567</v>
       </c>
-      <c r="F31" s="12"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B32" s="14" t="s">
-        <v>401</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>566</v>
-      </c>
-      <c r="E32" s="14" t="s">
-        <v>567</v>
-      </c>
-      <c r="F32" s="12"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>402</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D33" s="14" t="s">
+      <c r="E59" t="s">
+        <v>568</v>
+      </c>
+      <c r="F59" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G59" s="13"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>260</v>
+      </c>
+      <c r="B60" t="s">
+        <v>429</v>
+      </c>
+      <c r="C60" t="s">
+        <v>329</v>
+      </c>
+      <c r="D60" t="s">
+        <v>531</v>
+      </c>
+      <c r="E60" t="s">
+        <v>532</v>
+      </c>
+      <c r="F60" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G60" s="13"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>261</v>
+      </c>
+      <c r="B61" t="s">
+        <v>430</v>
+      </c>
+      <c r="C61" t="s">
+        <v>330</v>
+      </c>
+      <c r="D61" t="s">
+        <v>569</v>
+      </c>
+      <c r="E61" t="s">
+        <v>570</v>
+      </c>
+      <c r="F61" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G61" s="13"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>262</v>
+      </c>
+      <c r="B62" t="s">
+        <v>431</v>
+      </c>
+      <c r="C62" t="s">
+        <v>331</v>
+      </c>
+      <c r="D62" t="s">
+        <v>569</v>
+      </c>
+      <c r="E62" t="s">
+        <v>570</v>
+      </c>
+      <c r="F62" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G62" s="13"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>263</v>
+      </c>
+      <c r="B63" t="s">
+        <v>432</v>
+      </c>
+      <c r="C63" t="s">
+        <v>332</v>
+      </c>
+      <c r="D63" t="s">
+        <v>569</v>
+      </c>
+      <c r="E63" t="s">
+        <v>570</v>
+      </c>
+      <c r="F63" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G63" s="13"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>264</v>
+      </c>
+      <c r="B64" t="s">
+        <v>433</v>
+      </c>
+      <c r="C64" t="s">
+        <v>50</v>
+      </c>
+      <c r="D64" t="s">
         <v>525</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="E64" t="s">
         <v>526</v>
       </c>
-      <c r="F33" s="12"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>403</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="D34" s="14" t="s">
+      <c r="F64" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G64" s="13"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>135</v>
+      </c>
+      <c r="B65" t="s">
+        <v>434</v>
+      </c>
+      <c r="C65" t="s">
+        <v>163</v>
+      </c>
+      <c r="D65" t="s">
         <v>525</v>
       </c>
-      <c r="E34" s="14" t="s">
+      <c r="E65" t="s">
         <v>526</v>
       </c>
-      <c r="F34" s="12"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>404</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="D35" s="14" t="s">
+      <c r="F65" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G65" s="13"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>120</v>
+      </c>
+      <c r="B66" t="s">
+        <v>435</v>
+      </c>
+      <c r="C66" t="s">
+        <v>162</v>
+      </c>
+      <c r="D66" t="s">
         <v>525</v>
       </c>
-      <c r="E35" s="14" t="s">
+      <c r="E66" t="s">
         <v>526</v>
       </c>
-      <c r="F35" s="12"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="B36" s="14" t="s">
-        <v>405</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="D36" s="14" t="s">
+      <c r="F66" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G66" s="13"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>265</v>
+      </c>
+      <c r="B67" t="s">
+        <v>436</v>
+      </c>
+      <c r="C67" t="s">
+        <v>333</v>
+      </c>
+      <c r="D67" t="s">
         <v>525</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="E67" t="s">
         <v>526</v>
       </c>
-      <c r="F36" s="12"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="B37" s="14" t="s">
-        <v>406</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="D37" s="14" t="s">
+      <c r="F67" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G67" s="13"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>266</v>
+      </c>
+      <c r="B68" t="s">
+        <v>437</v>
+      </c>
+      <c r="C68" t="s">
+        <v>334</v>
+      </c>
+      <c r="D68" t="s">
         <v>525</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="E68" t="s">
         <v>526</v>
       </c>
-      <c r="F37" s="12"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>407</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="D38" s="14" t="s">
+      <c r="F68" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G68" s="13"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>267</v>
+      </c>
+      <c r="B69" t="s">
+        <v>438</v>
+      </c>
+      <c r="C69" t="s">
+        <v>335</v>
+      </c>
+      <c r="D69" t="s">
         <v>525</v>
       </c>
-      <c r="E38" s="14" t="s">
+      <c r="E69" t="s">
         <v>526</v>
       </c>
-      <c r="F38" s="12"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="B39" s="14" t="s">
-        <v>408</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="D39" s="14" t="s">
+      <c r="F69" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G69" s="13"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>268</v>
+      </c>
+      <c r="B70" t="s">
+        <v>439</v>
+      </c>
+      <c r="C70" t="s">
+        <v>336</v>
+      </c>
+      <c r="D70" t="s">
         <v>525</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="E70" t="s">
         <v>526</v>
       </c>
-      <c r="F39" s="12"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B40" s="14" t="s">
-        <v>409</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="D40" s="14" t="s">
+      <c r="F70" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G70" s="13"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>269</v>
+      </c>
+      <c r="B71" t="s">
+        <v>440</v>
+      </c>
+      <c r="C71" t="s">
+        <v>337</v>
+      </c>
+      <c r="D71" t="s">
         <v>525</v>
       </c>
-      <c r="E40" s="14" t="s">
+      <c r="E71" t="s">
         <v>526</v>
       </c>
-      <c r="F40" s="12"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B41" s="14" t="s">
-        <v>410</v>
-      </c>
-      <c r="C41" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D41" s="14" t="s">
+      <c r="F71" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G71" s="13"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>270</v>
+      </c>
+      <c r="B72" t="s">
+        <v>441</v>
+      </c>
+      <c r="C72" t="s">
+        <v>338</v>
+      </c>
+      <c r="D72" t="s">
+        <v>525</v>
+      </c>
+      <c r="E72" t="s">
+        <v>526</v>
+      </c>
+      <c r="F72" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G72" s="13"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>271</v>
+      </c>
+      <c r="B73" t="s">
+        <v>442</v>
+      </c>
+      <c r="C73" t="s">
+        <v>339</v>
+      </c>
+      <c r="D73" t="s">
+        <v>525</v>
+      </c>
+      <c r="E73" t="s">
+        <v>526</v>
+      </c>
+      <c r="F73" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G73" s="13"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>272</v>
+      </c>
+      <c r="B74" t="s">
+        <v>443</v>
+      </c>
+      <c r="C74" t="s">
+        <v>340</v>
+      </c>
+      <c r="D74" t="s">
+        <v>525</v>
+      </c>
+      <c r="E74" t="s">
+        <v>526</v>
+      </c>
+      <c r="F74" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G74" s="13"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>273</v>
+      </c>
+      <c r="B75" t="s">
+        <v>444</v>
+      </c>
+      <c r="C75" t="s">
+        <v>341</v>
+      </c>
+      <c r="D75" t="s">
+        <v>525</v>
+      </c>
+      <c r="E75" t="s">
+        <v>526</v>
+      </c>
+      <c r="F75" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G75" s="13"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>274</v>
+      </c>
+      <c r="B76" t="s">
+        <v>445</v>
+      </c>
+      <c r="C76" t="s">
+        <v>342</v>
+      </c>
+      <c r="D76" t="s">
+        <v>525</v>
+      </c>
+      <c r="E76" t="s">
+        <v>526</v>
+      </c>
+      <c r="F76" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G76" s="13"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>275</v>
+      </c>
+      <c r="B77" t="s">
+        <v>446</v>
+      </c>
+      <c r="C77" t="s">
+        <v>343</v>
+      </c>
+      <c r="D77" t="s">
+        <v>525</v>
+      </c>
+      <c r="E77" t="s">
+        <v>526</v>
+      </c>
+      <c r="F77" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G77" s="13"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>276</v>
+      </c>
+      <c r="B78" t="s">
+        <v>447</v>
+      </c>
+      <c r="C78" t="s">
+        <v>165</v>
+      </c>
+      <c r="D78" t="s">
+        <v>525</v>
+      </c>
+      <c r="E78" t="s">
+        <v>526</v>
+      </c>
+      <c r="F78" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G78" s="13"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>277</v>
+      </c>
+      <c r="B79" t="s">
+        <v>448</v>
+      </c>
+      <c r="C79" t="s">
+        <v>344</v>
+      </c>
+      <c r="D79" t="s">
+        <v>525</v>
+      </c>
+      <c r="E79" t="s">
+        <v>526</v>
+      </c>
+      <c r="F79" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G79" s="13"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>278</v>
+      </c>
+      <c r="B80" t="s">
+        <v>449</v>
+      </c>
+      <c r="C80" t="s">
+        <v>345</v>
+      </c>
+      <c r="D80" t="s">
+        <v>525</v>
+      </c>
+      <c r="E80" t="s">
+        <v>526</v>
+      </c>
+      <c r="F80" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G80" s="13"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>279</v>
+      </c>
+      <c r="B81" t="s">
+        <v>450</v>
+      </c>
+      <c r="C81" t="s">
+        <v>346</v>
+      </c>
+      <c r="D81" t="s">
+        <v>525</v>
+      </c>
+      <c r="E81" t="s">
+        <v>526</v>
+      </c>
+      <c r="F81" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G81" s="13"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>280</v>
+      </c>
+      <c r="B82" t="s">
+        <v>451</v>
+      </c>
+      <c r="C82" t="s">
+        <v>51</v>
+      </c>
+      <c r="D82" t="s">
+        <v>525</v>
+      </c>
+      <c r="E82" t="s">
+        <v>526</v>
+      </c>
+      <c r="F82" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G82" s="13"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>121</v>
+      </c>
+      <c r="B83" t="s">
+        <v>452</v>
+      </c>
+      <c r="C83" t="s">
+        <v>166</v>
+      </c>
+      <c r="D83" t="s">
+        <v>525</v>
+      </c>
+      <c r="E83" t="s">
+        <v>526</v>
+      </c>
+      <c r="F83" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G83" s="13"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>281</v>
+      </c>
+      <c r="B84" t="s">
+        <v>453</v>
+      </c>
+      <c r="C84" t="s">
+        <v>53</v>
+      </c>
+      <c r="D84" t="s">
+        <v>525</v>
+      </c>
+      <c r="E84" t="s">
+        <v>526</v>
+      </c>
+      <c r="F84" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G84" s="13"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>282</v>
+      </c>
+      <c r="B85" t="s">
+        <v>454</v>
+      </c>
+      <c r="C85" t="s">
+        <v>54</v>
+      </c>
+      <c r="D85" t="s">
+        <v>525</v>
+      </c>
+      <c r="E85" t="s">
+        <v>526</v>
+      </c>
+      <c r="F85" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G85" s="13"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>112</v>
+      </c>
+      <c r="B86" t="s">
+        <v>455</v>
+      </c>
+      <c r="C86" t="s">
+        <v>137</v>
+      </c>
+      <c r="D86" t="s">
+        <v>525</v>
+      </c>
+      <c r="E86" t="s">
+        <v>526</v>
+      </c>
+      <c r="F86" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G86" s="13"/>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>283</v>
+      </c>
+      <c r="B87" t="s">
+        <v>456</v>
+      </c>
+      <c r="C87" t="s">
+        <v>57</v>
+      </c>
+      <c r="D87" t="s">
+        <v>525</v>
+      </c>
+      <c r="E87" t="s">
+        <v>526</v>
+      </c>
+      <c r="F87" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G87" s="13"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>284</v>
+      </c>
+      <c r="B88" t="s">
+        <v>457</v>
+      </c>
+      <c r="C88" t="s">
+        <v>139</v>
+      </c>
+      <c r="D88" t="s">
+        <v>525</v>
+      </c>
+      <c r="E88" t="s">
+        <v>526</v>
+      </c>
+      <c r="F88" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G88" s="13"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>131</v>
+      </c>
+      <c r="B89" t="s">
+        <v>458</v>
+      </c>
+      <c r="C89" t="s">
+        <v>140</v>
+      </c>
+      <c r="D89" t="s">
+        <v>525</v>
+      </c>
+      <c r="E89" t="s">
+        <v>526</v>
+      </c>
+      <c r="F89" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G89" s="13"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>132</v>
+      </c>
+      <c r="B90" t="s">
+        <v>459</v>
+      </c>
+      <c r="C90" t="s">
+        <v>141</v>
+      </c>
+      <c r="D90" t="s">
+        <v>525</v>
+      </c>
+      <c r="E90" t="s">
+        <v>526</v>
+      </c>
+      <c r="F90" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G90" s="13"/>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>118</v>
+      </c>
+      <c r="B91" t="s">
+        <v>460</v>
+      </c>
+      <c r="C91" t="s">
+        <v>142</v>
+      </c>
+      <c r="D91" t="s">
+        <v>525</v>
+      </c>
+      <c r="E91" t="s">
+        <v>526</v>
+      </c>
+      <c r="F91" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G91" s="13"/>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>285</v>
+      </c>
+      <c r="B92" t="s">
+        <v>461</v>
+      </c>
+      <c r="C92" t="s">
+        <v>73</v>
+      </c>
+      <c r="D92" t="s">
+        <v>525</v>
+      </c>
+      <c r="E92" t="s">
+        <v>526</v>
+      </c>
+      <c r="F92" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G92" s="13"/>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>286</v>
+      </c>
+      <c r="B93" t="s">
+        <v>462</v>
+      </c>
+      <c r="C93" t="s">
+        <v>77</v>
+      </c>
+      <c r="D93" t="s">
+        <v>525</v>
+      </c>
+      <c r="E93" t="s">
+        <v>526</v>
+      </c>
+      <c r="F93" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G93" s="13"/>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>287</v>
+      </c>
+      <c r="B94" t="s">
+        <v>463</v>
+      </c>
+      <c r="C94" t="s">
+        <v>347</v>
+      </c>
+      <c r="D94" t="s">
+        <v>525</v>
+      </c>
+      <c r="E94" t="s">
+        <v>526</v>
+      </c>
+      <c r="F94" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G94" s="13"/>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>288</v>
+      </c>
+      <c r="B95" t="s">
+        <v>464</v>
+      </c>
+      <c r="C95" t="s">
+        <v>76</v>
+      </c>
+      <c r="D95" t="s">
+        <v>525</v>
+      </c>
+      <c r="E95" t="s">
+        <v>526</v>
+      </c>
+      <c r="F95" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G95" s="13"/>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>289</v>
+      </c>
+      <c r="B96" t="s">
+        <v>465</v>
+      </c>
+      <c r="C96" t="s">
+        <v>79</v>
+      </c>
+      <c r="D96" t="s">
+        <v>525</v>
+      </c>
+      <c r="E96" t="s">
+        <v>526</v>
+      </c>
+      <c r="F96" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G96" s="13"/>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>111</v>
+      </c>
+      <c r="B97" t="s">
+        <v>466</v>
+      </c>
+      <c r="C97" t="s">
+        <v>144</v>
+      </c>
+      <c r="D97" t="s">
+        <v>525</v>
+      </c>
+      <c r="E97" t="s">
+        <v>526</v>
+      </c>
+      <c r="F97" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G97" s="13"/>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>123</v>
+      </c>
+      <c r="B98" t="s">
+        <v>467</v>
+      </c>
+      <c r="C98" t="s">
+        <v>149</v>
+      </c>
+      <c r="D98" t="s">
+        <v>525</v>
+      </c>
+      <c r="E98" t="s">
+        <v>526</v>
+      </c>
+      <c r="F98" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G98" s="13"/>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>130</v>
+      </c>
+      <c r="B99" t="s">
+        <v>468</v>
+      </c>
+      <c r="C99" t="s">
+        <v>155</v>
+      </c>
+      <c r="D99" t="s">
+        <v>525</v>
+      </c>
+      <c r="E99" t="s">
+        <v>526</v>
+      </c>
+      <c r="F99" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G99" s="13"/>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>124</v>
+      </c>
+      <c r="B100" t="s">
+        <v>469</v>
+      </c>
+      <c r="C100" t="s">
+        <v>150</v>
+      </c>
+      <c r="D100" t="s">
+        <v>525</v>
+      </c>
+      <c r="E100" t="s">
+        <v>526</v>
+      </c>
+      <c r="F100" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G100" s="13"/>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>122</v>
+      </c>
+      <c r="B101" t="s">
+        <v>470</v>
+      </c>
+      <c r="C101" t="s">
+        <v>148</v>
+      </c>
+      <c r="D101" t="s">
+        <v>525</v>
+      </c>
+      <c r="E101" t="s">
+        <v>526</v>
+      </c>
+      <c r="F101" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G101" s="13"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>129</v>
+      </c>
+      <c r="B102" t="s">
+        <v>471</v>
+      </c>
+      <c r="C102" t="s">
+        <v>154</v>
+      </c>
+      <c r="D102" t="s">
+        <v>525</v>
+      </c>
+      <c r="E102" t="s">
+        <v>526</v>
+      </c>
+      <c r="F102" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G102" s="13"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>134</v>
+      </c>
+      <c r="B103" t="s">
+        <v>472</v>
+      </c>
+      <c r="C103" t="s">
+        <v>157</v>
+      </c>
+      <c r="D103" t="s">
+        <v>525</v>
+      </c>
+      <c r="E103" t="s">
+        <v>526</v>
+      </c>
+      <c r="F103" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G103" s="13"/>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>109</v>
+      </c>
+      <c r="B104" t="s">
+        <v>473</v>
+      </c>
+      <c r="C104" t="s">
+        <v>145</v>
+      </c>
+      <c r="D104" t="s">
+        <v>525</v>
+      </c>
+      <c r="E104" t="s">
+        <v>526</v>
+      </c>
+      <c r="F104" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G104" s="13"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>133</v>
+      </c>
+      <c r="B105" t="s">
+        <v>474</v>
+      </c>
+      <c r="C105" t="s">
+        <v>156</v>
+      </c>
+      <c r="D105" t="s">
+        <v>525</v>
+      </c>
+      <c r="E105" t="s">
+        <v>526</v>
+      </c>
+      <c r="F105" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G105" s="13"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>116</v>
+      </c>
+      <c r="B106" t="s">
+        <v>475</v>
+      </c>
+      <c r="C106" t="s">
+        <v>146</v>
+      </c>
+      <c r="D106" t="s">
+        <v>525</v>
+      </c>
+      <c r="E106" t="s">
+        <v>526</v>
+      </c>
+      <c r="F106" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G106" s="13"/>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>128</v>
+      </c>
+      <c r="B107" t="s">
+        <v>476</v>
+      </c>
+      <c r="C107" t="s">
+        <v>153</v>
+      </c>
+      <c r="D107" t="s">
+        <v>525</v>
+      </c>
+      <c r="E107" t="s">
+        <v>526</v>
+      </c>
+      <c r="F107" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G107" s="13"/>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>127</v>
+      </c>
+      <c r="B108" t="s">
+        <v>477</v>
+      </c>
+      <c r="C108" t="s">
+        <v>152</v>
+      </c>
+      <c r="D108" t="s">
+        <v>525</v>
+      </c>
+      <c r="E108" t="s">
+        <v>526</v>
+      </c>
+      <c r="F108" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G108" s="13"/>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>126</v>
+      </c>
+      <c r="B109" t="s">
+        <v>478</v>
+      </c>
+      <c r="C109" t="s">
+        <v>151</v>
+      </c>
+      <c r="D109" t="s">
+        <v>525</v>
+      </c>
+      <c r="E109" t="s">
+        <v>526</v>
+      </c>
+      <c r="F109" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G109" s="13"/>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>117</v>
+      </c>
+      <c r="B110" t="s">
+        <v>479</v>
+      </c>
+      <c r="C110" t="s">
+        <v>147</v>
+      </c>
+      <c r="D110" t="s">
+        <v>525</v>
+      </c>
+      <c r="E110" t="s">
+        <v>526</v>
+      </c>
+      <c r="F110" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G110" s="13"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>125</v>
+      </c>
+      <c r="B111" t="s">
+        <v>480</v>
+      </c>
+      <c r="C111" t="s">
+        <v>158</v>
+      </c>
+      <c r="D111" t="s">
+        <v>525</v>
+      </c>
+      <c r="E111" t="s">
+        <v>526</v>
+      </c>
+      <c r="F111" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G111" s="13"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>290</v>
+      </c>
+      <c r="B112" t="s">
+        <v>481</v>
+      </c>
+      <c r="C112" t="s">
+        <v>81</v>
+      </c>
+      <c r="D112" t="s">
+        <v>525</v>
+      </c>
+      <c r="E112" t="s">
+        <v>526</v>
+      </c>
+      <c r="F112" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G112" s="13"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>110</v>
+      </c>
+      <c r="B113" t="s">
+        <v>482</v>
+      </c>
+      <c r="C113" t="s">
+        <v>159</v>
+      </c>
+      <c r="D113" t="s">
+        <v>525</v>
+      </c>
+      <c r="E113" t="s">
+        <v>526</v>
+      </c>
+      <c r="F113" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G113" s="13"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>114</v>
+      </c>
+      <c r="B114" t="s">
+        <v>483</v>
+      </c>
+      <c r="C114" t="s">
+        <v>160</v>
+      </c>
+      <c r="D114" t="s">
+        <v>525</v>
+      </c>
+      <c r="E114" t="s">
+        <v>526</v>
+      </c>
+      <c r="F114" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G114" s="13"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>119</v>
+      </c>
+      <c r="B115" t="s">
+        <v>484</v>
+      </c>
+      <c r="C115" t="s">
+        <v>161</v>
+      </c>
+      <c r="D115" t="s">
+        <v>525</v>
+      </c>
+      <c r="E115" t="s">
+        <v>526</v>
+      </c>
+      <c r="F115" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G115" s="13"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>291</v>
+      </c>
+      <c r="B116" t="s">
+        <v>485</v>
+      </c>
+      <c r="C116" t="s">
+        <v>89</v>
+      </c>
+      <c r="D116" t="s">
+        <v>525</v>
+      </c>
+      <c r="E116" t="s">
+        <v>526</v>
+      </c>
+      <c r="F116" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G116" s="13"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>292</v>
+      </c>
+      <c r="B117" t="s">
+        <v>486</v>
+      </c>
+      <c r="C117" t="s">
+        <v>90</v>
+      </c>
+      <c r="D117" t="s">
+        <v>525</v>
+      </c>
+      <c r="E117" t="s">
+        <v>526</v>
+      </c>
+      <c r="F117" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G117" s="13"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>107</v>
+      </c>
+      <c r="B118" t="s">
+        <v>487</v>
+      </c>
+      <c r="C118" t="s">
+        <v>164</v>
+      </c>
+      <c r="D118" t="s">
+        <v>525</v>
+      </c>
+      <c r="E118" t="s">
+        <v>526</v>
+      </c>
+      <c r="F118" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G118" s="13"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>293</v>
+      </c>
+      <c r="B119" t="s">
+        <v>488</v>
+      </c>
+      <c r="C119" t="s">
+        <v>571</v>
+      </c>
+      <c r="D119" t="s">
+        <v>572</v>
+      </c>
+      <c r="E119" t="s">
+        <v>573</v>
+      </c>
+      <c r="F119" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G119" s="13"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>294</v>
+      </c>
+      <c r="B120" t="s">
+        <v>489</v>
+      </c>
+      <c r="C120" t="s">
+        <v>574</v>
+      </c>
+      <c r="D120" t="s">
+        <v>572</v>
+      </c>
+      <c r="E120" t="s">
+        <v>573</v>
+      </c>
+      <c r="F120" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G120" s="13"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>295</v>
+      </c>
+      <c r="B121" t="s">
+        <v>490</v>
+      </c>
+      <c r="C121" t="s">
+        <v>575</v>
+      </c>
+      <c r="D121" t="s">
+        <v>572</v>
+      </c>
+      <c r="E121" t="s">
+        <v>573</v>
+      </c>
+      <c r="F121" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G121" s="13"/>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>296</v>
+      </c>
+      <c r="B122" t="s">
+        <v>491</v>
+      </c>
+      <c r="C122" t="s">
+        <v>576</v>
+      </c>
+      <c r="D122" t="s">
+        <v>572</v>
+      </c>
+      <c r="E122" t="s">
+        <v>573</v>
+      </c>
+      <c r="F122" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G122" s="13"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>297</v>
+      </c>
+      <c r="B123" t="s">
+        <v>492</v>
+      </c>
+      <c r="C123" t="s">
+        <v>577</v>
+      </c>
+      <c r="D123" t="s">
+        <v>572</v>
+      </c>
+      <c r="E123" t="s">
+        <v>573</v>
+      </c>
+      <c r="F123" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G123" s="13"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>298</v>
+      </c>
+      <c r="B124" t="s">
+        <v>493</v>
+      </c>
+      <c r="C124" t="s">
+        <v>578</v>
+      </c>
+      <c r="D124" t="s">
+        <v>572</v>
+      </c>
+      <c r="E124" t="s">
+        <v>573</v>
+      </c>
+      <c r="F124" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G124" s="13"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>299</v>
+      </c>
+      <c r="B125" t="s">
+        <v>494</v>
+      </c>
+      <c r="C125" t="s">
+        <v>579</v>
+      </c>
+      <c r="D125" t="s">
+        <v>572</v>
+      </c>
+      <c r="E125" t="s">
+        <v>573</v>
+      </c>
+      <c r="F125" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G125" s="13"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>300</v>
+      </c>
+      <c r="B126" t="s">
+        <v>495</v>
+      </c>
+      <c r="C126" t="s">
+        <v>580</v>
+      </c>
+      <c r="D126" t="s">
+        <v>572</v>
+      </c>
+      <c r="E126" t="s">
+        <v>573</v>
+      </c>
+      <c r="F126" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G126" s="13"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>301</v>
+      </c>
+      <c r="B127" t="s">
+        <v>496</v>
+      </c>
+      <c r="C127" t="s">
+        <v>581</v>
+      </c>
+      <c r="D127" t="s">
+        <v>572</v>
+      </c>
+      <c r="E127" t="s">
+        <v>573</v>
+      </c>
+      <c r="F127" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G127" s="13"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>302</v>
+      </c>
+      <c r="B128" t="s">
+        <v>497</v>
+      </c>
+      <c r="C128" t="s">
+        <v>582</v>
+      </c>
+      <c r="D128" t="s">
+        <v>572</v>
+      </c>
+      <c r="E128" t="s">
+        <v>573</v>
+      </c>
+      <c r="F128" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G128" s="13"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>303</v>
+      </c>
+      <c r="B129" t="s">
+        <v>498</v>
+      </c>
+      <c r="C129" t="s">
+        <v>583</v>
+      </c>
+      <c r="D129" t="s">
+        <v>572</v>
+      </c>
+      <c r="E129" t="s">
+        <v>573</v>
+      </c>
+      <c r="F129" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G129" s="13"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>304</v>
+      </c>
+      <c r="B130" t="s">
+        <v>499</v>
+      </c>
+      <c r="C130" t="s">
+        <v>584</v>
+      </c>
+      <c r="D130" t="s">
+        <v>572</v>
+      </c>
+      <c r="E130" t="s">
+        <v>573</v>
+      </c>
+      <c r="F130" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G130" s="13"/>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>305</v>
+      </c>
+      <c r="B131" t="s">
+        <v>500</v>
+      </c>
+      <c r="C131" t="s">
+        <v>585</v>
+      </c>
+      <c r="D131" t="s">
+        <v>572</v>
+      </c>
+      <c r="E131" t="s">
+        <v>573</v>
+      </c>
+      <c r="F131" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G131" s="13"/>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>306</v>
+      </c>
+      <c r="B132" t="s">
+        <v>501</v>
+      </c>
+      <c r="C132" t="s">
+        <v>348</v>
+      </c>
+      <c r="D132" t="s">
+        <v>537</v>
+      </c>
+      <c r="E132" t="s">
+        <v>538</v>
+      </c>
+      <c r="F132" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G132" s="13"/>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>307</v>
+      </c>
+      <c r="B133" t="s">
+        <v>502</v>
+      </c>
+      <c r="C133" t="s">
+        <v>349</v>
+      </c>
+      <c r="D133" t="s">
+        <v>537</v>
+      </c>
+      <c r="E133" t="s">
+        <v>538</v>
+      </c>
+      <c r="F133" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G133" s="13"/>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>308</v>
+      </c>
+      <c r="B134" t="s">
+        <v>503</v>
+      </c>
+      <c r="C134" t="s">
+        <v>350</v>
+      </c>
+      <c r="D134" t="s">
+        <v>537</v>
+      </c>
+      <c r="E134" t="s">
+        <v>538</v>
+      </c>
+      <c r="F134" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G134" s="13"/>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>309</v>
+      </c>
+      <c r="B135" t="s">
+        <v>504</v>
+      </c>
+      <c r="C135" t="s">
+        <v>351</v>
+      </c>
+      <c r="D135" t="s">
+        <v>537</v>
+      </c>
+      <c r="E135" t="s">
+        <v>538</v>
+      </c>
+      <c r="F135" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G135" s="13"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>310</v>
+      </c>
+      <c r="B136" t="s">
+        <v>505</v>
+      </c>
+      <c r="C136" t="s">
+        <v>352</v>
+      </c>
+      <c r="D136" t="s">
+        <v>537</v>
+      </c>
+      <c r="E136" t="s">
+        <v>538</v>
+      </c>
+      <c r="F136" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G136" s="13"/>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
+        <v>311</v>
+      </c>
+      <c r="B137" t="s">
+        <v>506</v>
+      </c>
+      <c r="C137" t="s">
+        <v>353</v>
+      </c>
+      <c r="D137" t="s">
+        <v>537</v>
+      </c>
+      <c r="E137" t="s">
+        <v>538</v>
+      </c>
+      <c r="F137" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G137" s="13"/>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>312</v>
+      </c>
+      <c r="B138" t="s">
+        <v>507</v>
+      </c>
+      <c r="C138" t="s">
+        <v>354</v>
+      </c>
+      <c r="D138" t="s">
+        <v>537</v>
+      </c>
+      <c r="E138" t="s">
+        <v>538</v>
+      </c>
+      <c r="F138" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G138" s="13"/>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>313</v>
+      </c>
+      <c r="B139" t="s">
+        <v>508</v>
+      </c>
+      <c r="C139" t="s">
+        <v>355</v>
+      </c>
+      <c r="D139" t="s">
+        <v>537</v>
+      </c>
+      <c r="E139" t="s">
+        <v>538</v>
+      </c>
+      <c r="F139" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G139" s="13"/>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>314</v>
+      </c>
+      <c r="B140" t="s">
+        <v>509</v>
+      </c>
+      <c r="C140" t="s">
+        <v>356</v>
+      </c>
+      <c r="D140" t="s">
+        <v>537</v>
+      </c>
+      <c r="E140" t="s">
+        <v>538</v>
+      </c>
+      <c r="F140" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G140" s="13"/>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>315</v>
+      </c>
+      <c r="B141" t="s">
+        <v>510</v>
+      </c>
+      <c r="C141" t="s">
+        <v>357</v>
+      </c>
+      <c r="D141" t="s">
+        <v>537</v>
+      </c>
+      <c r="E141" t="s">
+        <v>538</v>
+      </c>
+      <c r="F141" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G141" s="13"/>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>316</v>
+      </c>
+      <c r="B142" t="s">
+        <v>511</v>
+      </c>
+      <c r="C142" t="s">
+        <v>358</v>
+      </c>
+      <c r="D142" t="s">
+        <v>537</v>
+      </c>
+      <c r="E142" t="s">
+        <v>538</v>
+      </c>
+      <c r="F142" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G142" s="13"/>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>317</v>
+      </c>
+      <c r="B143" t="s">
+        <v>512</v>
+      </c>
+      <c r="C143" t="s">
+        <v>359</v>
+      </c>
+      <c r="D143" t="s">
+        <v>537</v>
+      </c>
+      <c r="E143" t="s">
+        <v>538</v>
+      </c>
+      <c r="F143" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G143" s="13"/>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>318</v>
+      </c>
+      <c r="B144" t="s">
+        <v>513</v>
+      </c>
+      <c r="C144" t="s">
+        <v>360</v>
+      </c>
+      <c r="D144" t="s">
+        <v>537</v>
+      </c>
+      <c r="E144" t="s">
+        <v>538</v>
+      </c>
+      <c r="F144" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G144" s="13"/>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>319</v>
+      </c>
+      <c r="B145" t="s">
+        <v>514</v>
+      </c>
+      <c r="C145" t="s">
+        <v>361</v>
+      </c>
+      <c r="D145" t="s">
+        <v>537</v>
+      </c>
+      <c r="E145" t="s">
+        <v>538</v>
+      </c>
+      <c r="F145" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G145" s="13"/>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>320</v>
+      </c>
+      <c r="B146" t="s">
+        <v>515</v>
+      </c>
+      <c r="C146" t="s">
+        <v>320</v>
+      </c>
+      <c r="D146" t="s">
+        <v>537</v>
+      </c>
+      <c r="E146" t="s">
+        <v>538</v>
+      </c>
+      <c r="F146" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G146" s="13"/>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A147" t="s">
+        <v>321</v>
+      </c>
+      <c r="B147" t="s">
+        <v>516</v>
+      </c>
+      <c r="C147" t="s">
+        <v>362</v>
+      </c>
+      <c r="D147" t="s">
         <v>531</v>
       </c>
-      <c r="E41" s="14" t="s">
+      <c r="E147" t="s">
         <v>532</v>
       </c>
-      <c r="F41" s="12"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="13"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B42" s="14" t="s">
-        <v>411</v>
-      </c>
-      <c r="C42" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D42" s="14" t="s">
+      <c r="F147" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G147" s="13"/>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A148" t="s">
+        <v>322</v>
+      </c>
+      <c r="B148" t="s">
+        <v>517</v>
+      </c>
+      <c r="C148" t="s">
+        <v>363</v>
+      </c>
+      <c r="D148" t="s">
         <v>537</v>
       </c>
-      <c r="E42" s="14" t="s">
+      <c r="E148" t="s">
         <v>538</v>
       </c>
-      <c r="F42" s="12"/>
-      <c r="G42" s="13"/>
-      <c r="H42" s="13"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="14" t="s">
-        <v>412</v>
-      </c>
-      <c r="C43" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="D43" s="14" t="s">
+      <c r="F148" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G148" s="13"/>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A149" t="s">
+        <v>323</v>
+      </c>
+      <c r="B149" t="s">
+        <v>518</v>
+      </c>
+      <c r="C149" t="s">
+        <v>586</v>
+      </c>
+      <c r="D149" t="s">
         <v>537</v>
       </c>
-      <c r="E43" s="14" t="s">
+      <c r="E149" t="s">
         <v>538</v>
       </c>
-      <c r="F43" s="12"/>
-      <c r="G43" s="13"/>
-      <c r="H43" s="13"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="14" t="s">
-        <v>413</v>
-      </c>
-      <c r="C44" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="D44" s="14" t="s">
+      <c r="F149" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G149" s="13"/>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A150" t="s">
+        <v>324</v>
+      </c>
+      <c r="B150" t="s">
+        <v>519</v>
+      </c>
+      <c r="C150" t="s">
+        <v>364</v>
+      </c>
+      <c r="D150" t="s">
         <v>537</v>
       </c>
-      <c r="E44" s="14" t="s">
+      <c r="E150" t="s">
         <v>538</v>
       </c>
-      <c r="F44" s="12"/>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="14" t="s">
-        <v>414</v>
-      </c>
-      <c r="C45" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="D45" s="14" t="s">
+      <c r="F150" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G150" s="13"/>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
+        <v>325</v>
+      </c>
+      <c r="B151" t="s">
+        <v>520</v>
+      </c>
+      <c r="C151" t="s">
+        <v>365</v>
+      </c>
+      <c r="D151" t="s">
         <v>537</v>
       </c>
-      <c r="E45" s="14" t="s">
+      <c r="E151" t="s">
         <v>538</v>
       </c>
-      <c r="F45" s="12"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="14" t="s">
-        <v>415</v>
-      </c>
-      <c r="C46" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="D46" s="14" t="s">
+      <c r="F151" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G151" s="13"/>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A152" t="s">
+        <v>326</v>
+      </c>
+      <c r="B152" t="s">
+        <v>521</v>
+      </c>
+      <c r="C152" t="s">
+        <v>368</v>
+      </c>
+      <c r="D152" t="s">
         <v>537</v>
       </c>
-      <c r="E46" s="14" t="s">
+      <c r="E152" t="s">
         <v>538</v>
       </c>
-      <c r="F46" s="12"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A47" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="14" t="s">
-        <v>416</v>
-      </c>
-      <c r="C47" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="D47" s="14" t="s">
+      <c r="F152" s="14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A153" t="s">
+        <v>327</v>
+      </c>
+      <c r="B153" t="s">
+        <v>522</v>
+      </c>
+      <c r="C153" t="s">
+        <v>366</v>
+      </c>
+      <c r="D153" t="s">
         <v>537</v>
       </c>
-      <c r="E47" s="14" t="s">
+      <c r="E153" t="s">
         <v>538</v>
       </c>
-      <c r="F47" s="12"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="14" t="s">
-        <v>417</v>
-      </c>
-      <c r="C48" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="D48" s="14" t="s">
+      <c r="F153" s="14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A154" t="s">
+        <v>328</v>
+      </c>
+      <c r="B154" t="s">
+        <v>523</v>
+      </c>
+      <c r="C154" t="s">
+        <v>367</v>
+      </c>
+      <c r="D154" t="s">
         <v>537</v>
       </c>
-      <c r="E48" s="14" t="s">
+      <c r="E154" t="s">
         <v>538</v>
       </c>
-      <c r="F48" s="12"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="B49" s="14" t="s">
-        <v>418</v>
-      </c>
-      <c r="C49" s="14" t="s">
-        <v>230</v>
-      </c>
-      <c r="D49" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="E49" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="F49" s="12"/>
-      <c r="G49" s="13"/>
-      <c r="H49" s="13"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A50" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="B50" s="14" t="s">
-        <v>419</v>
-      </c>
-      <c r="C50" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="D50" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="E50" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="F50" s="12"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="13"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A51" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B51" s="14" t="s">
-        <v>420</v>
-      </c>
-      <c r="C51" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="D51" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="E51" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="F51" s="12"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="13"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A52" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52" s="14" t="s">
-        <v>421</v>
-      </c>
-      <c r="C52" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="D52" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="E52" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="F52" s="12"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="13"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A53" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B53" s="14" t="s">
-        <v>422</v>
-      </c>
-      <c r="C53" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="D53" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="E53" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="F53" s="12"/>
-      <c r="G53" s="13"/>
-      <c r="H53" s="13"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A54" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B54" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="C54" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="D54" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="E54" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="F54" s="12"/>
-      <c r="G54" s="13"/>
-      <c r="H54" s="13"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A55" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B55" s="14" t="s">
-        <v>424</v>
-      </c>
-      <c r="C55" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="D55" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="E55" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="F55" s="12"/>
-      <c r="G55" s="13"/>
-      <c r="H55" s="13"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A56" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B56" s="14" t="s">
-        <v>425</v>
-      </c>
-      <c r="C56" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="D56" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="E56" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="F56" s="12"/>
-      <c r="G56" s="13"/>
-      <c r="H56" s="13"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A57" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="B57" s="14" t="s">
-        <v>426</v>
-      </c>
-      <c r="C57" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="D57" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E57" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F57" s="12"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="13"/>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A58" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="B58" s="14" t="s">
-        <v>427</v>
-      </c>
-      <c r="C58" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="D58" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E58" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F58" s="12"/>
-      <c r="G58" s="13"/>
-      <c r="H58" s="13"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A59" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="B59" s="14" t="s">
-        <v>428</v>
-      </c>
-      <c r="C59" s="14" t="s">
-        <v>568</v>
-      </c>
-      <c r="D59" s="14" t="s">
-        <v>570</v>
-      </c>
-      <c r="E59" s="14" t="s">
-        <v>571</v>
-      </c>
-      <c r="F59" s="12"/>
-      <c r="G59" s="13"/>
-      <c r="H59" s="13"/>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A60" s="14"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14" t="s">
-        <v>569</v>
-      </c>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="12"/>
-      <c r="G60" s="13"/>
-      <c r="H60" s="13"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A61" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="B61" s="14" t="s">
-        <v>429</v>
-      </c>
-      <c r="C61" s="14" t="s">
-        <v>329</v>
-      </c>
-      <c r="D61" s="14" t="s">
-        <v>531</v>
-      </c>
-      <c r="E61" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="F61" s="12"/>
-      <c r="G61" s="13"/>
-      <c r="H61" s="13"/>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A62" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="B62" s="14" t="s">
-        <v>430</v>
-      </c>
-      <c r="C62" s="14" t="s">
-        <v>330</v>
-      </c>
-      <c r="D62" s="14" t="s">
-        <v>572</v>
-      </c>
-      <c r="E62" s="14" t="s">
-        <v>573</v>
-      </c>
-      <c r="F62" s="12"/>
-      <c r="G62" s="13"/>
-      <c r="H62" s="13"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A63" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="B63" s="14" t="s">
-        <v>431</v>
-      </c>
-      <c r="C63" s="14" t="s">
-        <v>331</v>
-      </c>
-      <c r="D63" s="14" t="s">
-        <v>572</v>
-      </c>
-      <c r="E63" s="14" t="s">
-        <v>573</v>
-      </c>
-      <c r="F63" s="12"/>
-      <c r="G63" s="13"/>
-      <c r="H63" s="13"/>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A64" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="B64" s="14" t="s">
-        <v>432</v>
-      </c>
-      <c r="C64" s="14" t="s">
-        <v>332</v>
-      </c>
-      <c r="D64" s="14" t="s">
-        <v>572</v>
-      </c>
-      <c r="E64" s="14" t="s">
-        <v>573</v>
-      </c>
-      <c r="F64" s="12"/>
-      <c r="G64" s="13"/>
-      <c r="H64" s="13"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A65" s="14" t="s">
-        <v>264</v>
-      </c>
-      <c r="B65" s="14" t="s">
-        <v>433</v>
-      </c>
-      <c r="C65" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D65" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E65" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F65" s="12"/>
-      <c r="G65" s="13"/>
-      <c r="H65" s="13"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A66" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="B66" s="14" t="s">
-        <v>434</v>
-      </c>
-      <c r="C66" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="D66" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E66" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F66" s="12"/>
-      <c r="G66" s="13"/>
-      <c r="H66" s="13"/>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A67" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="B67" s="14" t="s">
-        <v>435</v>
-      </c>
-      <c r="C67" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="D67" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E67" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F67" s="12"/>
-      <c r="G67" s="13"/>
-      <c r="H67" s="13"/>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A68" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="B68" s="14" t="s">
-        <v>436</v>
-      </c>
-      <c r="C68" s="14" t="s">
-        <v>333</v>
-      </c>
-      <c r="D68" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E68" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F68" s="12"/>
-      <c r="G68" s="13"/>
-      <c r="H68" s="13"/>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A69" s="14" t="s">
-        <v>266</v>
-      </c>
-      <c r="B69" s="14" t="s">
-        <v>437</v>
-      </c>
-      <c r="C69" s="14" t="s">
-        <v>334</v>
-      </c>
-      <c r="D69" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E69" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F69" s="12"/>
-      <c r="G69" s="13"/>
-      <c r="H69" s="13"/>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A70" s="14" t="s">
-        <v>267</v>
-      </c>
-      <c r="B70" s="14" t="s">
-        <v>438</v>
-      </c>
-      <c r="C70" s="14" t="s">
-        <v>335</v>
-      </c>
-      <c r="D70" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E70" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F70" s="12"/>
-      <c r="G70" s="13"/>
-      <c r="H70" s="13"/>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A71" s="14" t="s">
-        <v>268</v>
-      </c>
-      <c r="B71" s="14" t="s">
-        <v>439</v>
-      </c>
-      <c r="C71" s="14" t="s">
-        <v>336</v>
-      </c>
-      <c r="D71" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E71" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F71" s="12"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="13"/>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A72" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="B72" s="14" t="s">
-        <v>440</v>
-      </c>
-      <c r="C72" s="14" t="s">
-        <v>337</v>
-      </c>
-      <c r="D72" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E72" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F72" s="12"/>
-      <c r="G72" s="13"/>
-      <c r="H72" s="13"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A73" s="14" t="s">
-        <v>270</v>
-      </c>
-      <c r="B73" s="14" t="s">
-        <v>441</v>
-      </c>
-      <c r="C73" s="14" t="s">
-        <v>338</v>
-      </c>
-      <c r="D73" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E73" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F73" s="12"/>
-      <c r="G73" s="13"/>
-      <c r="H73" s="13"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A74" s="14" t="s">
-        <v>271</v>
-      </c>
-      <c r="B74" s="14" t="s">
-        <v>442</v>
-      </c>
-      <c r="C74" s="14" t="s">
-        <v>339</v>
-      </c>
-      <c r="D74" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E74" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F74" s="12"/>
-      <c r="G74" s="13"/>
-      <c r="H74" s="13"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A75" s="14" t="s">
-        <v>272</v>
-      </c>
-      <c r="B75" s="14" t="s">
-        <v>443</v>
-      </c>
-      <c r="C75" s="14" t="s">
-        <v>340</v>
-      </c>
-      <c r="D75" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E75" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F75" s="12"/>
-      <c r="G75" s="13"/>
-      <c r="H75" s="13"/>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A76" s="14" t="s">
-        <v>273</v>
-      </c>
-      <c r="B76" s="14" t="s">
-        <v>444</v>
-      </c>
-      <c r="C76" s="14" t="s">
-        <v>341</v>
-      </c>
-      <c r="D76" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E76" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F76" s="12"/>
-      <c r="G76" s="13"/>
-      <c r="H76" s="13"/>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A77" s="14" t="s">
-        <v>274</v>
-      </c>
-      <c r="B77" s="14" t="s">
-        <v>445</v>
-      </c>
-      <c r="C77" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="D77" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E77" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F77" s="12"/>
-      <c r="G77" s="13"/>
-      <c r="H77" s="13"/>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A78" s="14" t="s">
-        <v>275</v>
-      </c>
-      <c r="B78" s="14" t="s">
-        <v>446</v>
-      </c>
-      <c r="C78" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="D78" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E78" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F78" s="12"/>
-      <c r="G78" s="13"/>
-      <c r="H78" s="13"/>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A79" s="14" t="s">
-        <v>276</v>
-      </c>
-      <c r="B79" s="14" t="s">
-        <v>447</v>
-      </c>
-      <c r="C79" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="D79" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E79" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F79" s="12"/>
-      <c r="G79" s="13"/>
-      <c r="H79" s="13"/>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A80" s="14" t="s">
-        <v>277</v>
-      </c>
-      <c r="B80" s="14" t="s">
-        <v>448</v>
-      </c>
-      <c r="C80" s="14" t="s">
-        <v>344</v>
-      </c>
-      <c r="D80" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E80" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F80" s="12"/>
-      <c r="G80" s="13"/>
-      <c r="H80" s="13"/>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A81" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="B81" s="14" t="s">
-        <v>449</v>
-      </c>
-      <c r="C81" s="14" t="s">
-        <v>345</v>
-      </c>
-      <c r="D81" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E81" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F81" s="12"/>
-      <c r="G81" s="13"/>
-      <c r="H81" s="13"/>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A82" s="14" t="s">
-        <v>279</v>
-      </c>
-      <c r="B82" s="14" t="s">
-        <v>450</v>
-      </c>
-      <c r="C82" s="14" t="s">
-        <v>346</v>
-      </c>
-      <c r="D82" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E82" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F82" s="12"/>
-      <c r="G82" s="13"/>
-      <c r="H82" s="13"/>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A83" s="14" t="s">
-        <v>280</v>
-      </c>
-      <c r="B83" s="14" t="s">
-        <v>451</v>
-      </c>
-      <c r="C83" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D83" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E83" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F83" s="12"/>
-      <c r="G83" s="13"/>
-      <c r="H83" s="13"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A84" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="B84" s="14" t="s">
-        <v>452</v>
-      </c>
-      <c r="C84" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="D84" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E84" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F84" s="12"/>
-      <c r="G84" s="13"/>
-      <c r="H84" s="13"/>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A85" s="14" t="s">
-        <v>281</v>
-      </c>
-      <c r="B85" s="14" t="s">
-        <v>453</v>
-      </c>
-      <c r="C85" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="D85" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E85" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F85" s="12"/>
-      <c r="G85" s="13"/>
-      <c r="H85" s="13"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A86" s="14" t="s">
-        <v>282</v>
-      </c>
-      <c r="B86" s="14" t="s">
-        <v>454</v>
-      </c>
-      <c r="C86" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="D86" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E86" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F86" s="12"/>
-      <c r="G86" s="13"/>
-      <c r="H86" s="13"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A87" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="B87" s="14" t="s">
-        <v>455</v>
-      </c>
-      <c r="C87" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="D87" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E87" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F87" s="12"/>
-      <c r="G87" s="13"/>
-      <c r="H87" s="13"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A88" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="B88" s="14" t="s">
-        <v>456</v>
-      </c>
-      <c r="C88" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="D88" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E88" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F88" s="12"/>
-      <c r="G88" s="13"/>
-      <c r="H88" s="13"/>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A89" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="B89" s="14" t="s">
-        <v>457</v>
-      </c>
-      <c r="C89" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="D89" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E89" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F89" s="12"/>
-      <c r="G89" s="13"/>
-      <c r="H89" s="13"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A90" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="B90" s="14" t="s">
-        <v>458</v>
-      </c>
-      <c r="C90" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D90" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E90" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F90" s="12"/>
-      <c r="G90" s="13"/>
-      <c r="H90" s="13"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A91" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="B91" s="14" t="s">
-        <v>459</v>
-      </c>
-      <c r="C91" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="D91" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E91" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F91" s="12"/>
-      <c r="G91" s="13"/>
-      <c r="H91" s="13"/>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A92" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="B92" s="14" t="s">
-        <v>460</v>
-      </c>
-      <c r="C92" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="D92" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E92" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F92" s="12"/>
-      <c r="G92" s="13"/>
-      <c r="H92" s="13"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A93" s="14" t="s">
-        <v>285</v>
-      </c>
-      <c r="B93" s="14" t="s">
-        <v>461</v>
-      </c>
-      <c r="C93" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="D93" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E93" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F93" s="12"/>
-      <c r="G93" s="13"/>
-      <c r="H93" s="13"/>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A94" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="B94" s="14" t="s">
-        <v>462</v>
-      </c>
-      <c r="C94" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="D94" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E94" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F94" s="12"/>
-      <c r="G94" s="13"/>
-      <c r="H94" s="13"/>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A95" s="14" t="s">
-        <v>287</v>
-      </c>
-      <c r="B95" s="14" t="s">
-        <v>463</v>
-      </c>
-      <c r="C95" s="14" t="s">
-        <v>347</v>
-      </c>
-      <c r="D95" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E95" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F95" s="12"/>
-      <c r="G95" s="13"/>
-      <c r="H95" s="13"/>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A96" s="14" t="s">
-        <v>288</v>
-      </c>
-      <c r="B96" s="14" t="s">
-        <v>464</v>
-      </c>
-      <c r="C96" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="D96" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E96" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F96" s="12"/>
-      <c r="G96" s="13"/>
-      <c r="H96" s="13"/>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A97" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="B97" s="14" t="s">
-        <v>465</v>
-      </c>
-      <c r="C97" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="D97" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E97" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F97" s="12"/>
-      <c r="G97" s="13"/>
-      <c r="H97" s="13"/>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A98" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="B98" s="14" t="s">
-        <v>466</v>
-      </c>
-      <c r="C98" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="D98" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E98" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F98" s="12"/>
-      <c r="G98" s="13"/>
-      <c r="H98" s="13"/>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A99" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="B99" s="14" t="s">
-        <v>467</v>
-      </c>
-      <c r="C99" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="D99" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E99" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F99" s="12"/>
-      <c r="G99" s="13"/>
-      <c r="H99" s="13"/>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A100" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="B100" s="14" t="s">
-        <v>468</v>
-      </c>
-      <c r="C100" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="D100" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E100" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F100" s="12"/>
-      <c r="G100" s="13"/>
-      <c r="H100" s="13"/>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A101" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="B101" s="14" t="s">
-        <v>469</v>
-      </c>
-      <c r="C101" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="D101" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E101" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F101" s="12"/>
-      <c r="G101" s="13"/>
-      <c r="H101" s="13"/>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A102" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="B102" s="14" t="s">
-        <v>470</v>
-      </c>
-      <c r="C102" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="D102" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E102" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F102" s="12"/>
-      <c r="G102" s="13"/>
-      <c r="H102" s="13"/>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A103" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="B103" s="14" t="s">
-        <v>471</v>
-      </c>
-      <c r="C103" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="D103" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E103" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F103" s="12"/>
-      <c r="G103" s="13"/>
-      <c r="H103" s="13"/>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A104" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="B104" s="14" t="s">
-        <v>472</v>
-      </c>
-      <c r="C104" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="D104" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E104" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F104" s="12"/>
-      <c r="G104" s="13"/>
-      <c r="H104" s="13"/>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A105" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="B105" s="14" t="s">
-        <v>473</v>
-      </c>
-      <c r="C105" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="D105" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E105" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F105" s="12"/>
-      <c r="G105" s="13"/>
-      <c r="H105" s="13"/>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A106" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="B106" s="14" t="s">
-        <v>474</v>
-      </c>
-      <c r="C106" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="D106" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E106" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F106" s="12"/>
-      <c r="G106" s="13"/>
-      <c r="H106" s="13"/>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A107" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="B107" s="14" t="s">
-        <v>475</v>
-      </c>
-      <c r="C107" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="D107" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E107" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F107" s="12"/>
-      <c r="G107" s="13"/>
-      <c r="H107" s="13"/>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A108" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="B108" s="14" t="s">
-        <v>476</v>
-      </c>
-      <c r="C108" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="D108" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E108" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F108" s="12"/>
-      <c r="G108" s="13"/>
-      <c r="H108" s="13"/>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A109" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="B109" s="14" t="s">
-        <v>477</v>
-      </c>
-      <c r="C109" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="D109" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E109" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F109" s="12"/>
-      <c r="G109" s="13"/>
-      <c r="H109" s="13"/>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A110" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="B110" s="14" t="s">
-        <v>478</v>
-      </c>
-      <c r="C110" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="D110" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E110" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F110" s="12"/>
-      <c r="G110" s="13"/>
-      <c r="H110" s="13"/>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A111" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="B111" s="14" t="s">
-        <v>479</v>
-      </c>
-      <c r="C111" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="D111" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E111" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F111" s="12"/>
-      <c r="G111" s="13"/>
-      <c r="H111" s="13"/>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A112" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="B112" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="C112" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="D112" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E112" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F112" s="12"/>
-      <c r="G112" s="13"/>
-      <c r="H112" s="13"/>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A113" s="14" t="s">
-        <v>290</v>
-      </c>
-      <c r="B113" s="14" t="s">
-        <v>481</v>
-      </c>
-      <c r="C113" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="D113" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E113" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F113" s="12"/>
-      <c r="G113" s="13"/>
-      <c r="H113" s="13"/>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A114" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="B114" s="14" t="s">
-        <v>482</v>
-      </c>
-      <c r="C114" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="D114" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E114" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F114" s="12"/>
-      <c r="G114" s="13"/>
-      <c r="H114" s="13"/>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A115" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="B115" s="14" t="s">
-        <v>483</v>
-      </c>
-      <c r="C115" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="D115" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E115" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F115" s="12"/>
-      <c r="G115" s="13"/>
-      <c r="H115" s="13"/>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A116" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="B116" s="14" t="s">
-        <v>484</v>
-      </c>
-      <c r="C116" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="D116" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E116" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F116" s="12"/>
-      <c r="G116" s="13"/>
-      <c r="H116" s="13"/>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A117" s="14" t="s">
-        <v>291</v>
-      </c>
-      <c r="B117" s="14" t="s">
-        <v>485</v>
-      </c>
-      <c r="C117" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="D117" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E117" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F117" s="12"/>
-      <c r="G117" s="13"/>
-      <c r="H117" s="13"/>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A118" s="14" t="s">
-        <v>292</v>
-      </c>
-      <c r="B118" s="14" t="s">
-        <v>486</v>
-      </c>
-      <c r="C118" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="D118" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E118" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F118" s="12"/>
-      <c r="G118" s="13"/>
-      <c r="H118" s="13"/>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A119" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="B119" s="14" t="s">
-        <v>487</v>
-      </c>
-      <c r="C119" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="D119" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="E119" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="F119" s="12"/>
-      <c r="G119" s="13"/>
-      <c r="H119" s="13"/>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A120" s="14" t="s">
-        <v>293</v>
-      </c>
-      <c r="B120" s="14" t="s">
-        <v>488</v>
-      </c>
-      <c r="C120" s="14" t="s">
-        <v>574</v>
-      </c>
-      <c r="D120" s="14" t="s">
-        <v>575</v>
-      </c>
-      <c r="E120" s="14" t="s">
-        <v>576</v>
-      </c>
-      <c r="F120" s="12"/>
-      <c r="G120" s="13"/>
-      <c r="H120" s="13"/>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A121" s="14" t="s">
-        <v>294</v>
-      </c>
-      <c r="B121" s="14" t="s">
-        <v>489</v>
-      </c>
-      <c r="C121" s="14" t="s">
-        <v>577</v>
-      </c>
-      <c r="D121" s="14" t="s">
-        <v>575</v>
-      </c>
-      <c r="E121" s="14" t="s">
-        <v>576</v>
-      </c>
-      <c r="F121" s="12"/>
-      <c r="G121" s="13"/>
-      <c r="H121" s="13"/>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A122" s="14" t="s">
-        <v>295</v>
-      </c>
-      <c r="B122" s="14" t="s">
-        <v>490</v>
-      </c>
-      <c r="C122" s="14" t="s">
-        <v>578</v>
-      </c>
-      <c r="D122" s="14" t="s">
-        <v>575</v>
-      </c>
-      <c r="E122" s="14" t="s">
-        <v>576</v>
-      </c>
-      <c r="F122" s="12"/>
-      <c r="G122" s="13"/>
-      <c r="H122" s="13"/>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A123" s="14" t="s">
-        <v>296</v>
-      </c>
-      <c r="B123" s="14" t="s">
-        <v>491</v>
-      </c>
-      <c r="C123" s="14" t="s">
-        <v>579</v>
-      </c>
-      <c r="D123" s="14" t="s">
-        <v>575</v>
-      </c>
-      <c r="E123" s="14" t="s">
-        <v>576</v>
-      </c>
-      <c r="F123" s="12"/>
-      <c r="G123" s="13"/>
-      <c r="H123" s="13"/>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A124" s="14" t="s">
-        <v>297</v>
-      </c>
-      <c r="B124" s="14" t="s">
-        <v>492</v>
-      </c>
-      <c r="C124" s="14" t="s">
-        <v>580</v>
-      </c>
-      <c r="D124" s="14" t="s">
-        <v>575</v>
-      </c>
-      <c r="E124" s="14" t="s">
-        <v>576</v>
-      </c>
-      <c r="F124" s="12"/>
-      <c r="G124" s="13"/>
-      <c r="H124" s="13"/>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A125" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="B125" s="14" t="s">
-        <v>493</v>
-      </c>
-      <c r="C125" s="14" t="s">
-        <v>581</v>
-      </c>
-      <c r="D125" s="14" t="s">
-        <v>575</v>
-      </c>
-      <c r="E125" s="14" t="s">
-        <v>576</v>
-      </c>
-      <c r="F125" s="12"/>
-      <c r="G125" s="13"/>
-      <c r="H125" s="13"/>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A126" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="B126" s="14" t="s">
-        <v>494</v>
-      </c>
-      <c r="C126" s="14" t="s">
-        <v>582</v>
-      </c>
-      <c r="D126" s="14" t="s">
-        <v>575</v>
-      </c>
-      <c r="E126" s="14" t="s">
-        <v>576</v>
-      </c>
-      <c r="F126" s="12"/>
-      <c r="G126" s="13"/>
-      <c r="H126" s="13"/>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A127" s="14" t="s">
-        <v>300</v>
-      </c>
-      <c r="B127" s="14" t="s">
-        <v>495</v>
-      </c>
-      <c r="C127" s="14" t="s">
-        <v>583</v>
-      </c>
-      <c r="D127" s="14" t="s">
-        <v>575</v>
-      </c>
-      <c r="E127" s="14" t="s">
-        <v>576</v>
-      </c>
-      <c r="F127" s="12"/>
-      <c r="G127" s="13"/>
-      <c r="H127" s="13"/>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A128" s="14" t="s">
-        <v>301</v>
-      </c>
-      <c r="B128" s="14" t="s">
-        <v>496</v>
-      </c>
-      <c r="C128" s="14" t="s">
-        <v>584</v>
-      </c>
-      <c r="D128" s="14" t="s">
-        <v>575</v>
-      </c>
-      <c r="E128" s="14" t="s">
-        <v>576</v>
-      </c>
-      <c r="F128" s="12"/>
-      <c r="G128" s="13"/>
-      <c r="H128" s="13"/>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A129" s="14" t="s">
-        <v>302</v>
-      </c>
-      <c r="B129" s="14" t="s">
-        <v>497</v>
-      </c>
-      <c r="C129" s="14" t="s">
-        <v>585</v>
-      </c>
-      <c r="D129" s="14" t="s">
-        <v>575</v>
-      </c>
-      <c r="E129" s="14" t="s">
-        <v>576</v>
-      </c>
-      <c r="F129" s="12"/>
-      <c r="G129" s="13"/>
-      <c r="H129" s="13"/>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A130" s="14" t="s">
-        <v>303</v>
-      </c>
-      <c r="B130" s="14" t="s">
-        <v>498</v>
-      </c>
-      <c r="C130" s="14" t="s">
-        <v>586</v>
-      </c>
-      <c r="D130" s="14" t="s">
-        <v>575</v>
-      </c>
-      <c r="E130" s="14" t="s">
-        <v>576</v>
-      </c>
-      <c r="F130" s="12"/>
-      <c r="G130" s="13"/>
-      <c r="H130" s="13"/>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A131" s="14" t="s">
-        <v>304</v>
-      </c>
-      <c r="B131" s="14" t="s">
-        <v>499</v>
-      </c>
-      <c r="C131" s="14" t="s">
+      <c r="F154" s="14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A155" s="11" t="s">
         <v>587</v>
       </c>
-      <c r="D131" s="14" t="s">
-        <v>575</v>
-      </c>
-      <c r="E131" s="14" t="s">
-        <v>576</v>
-      </c>
-      <c r="F131" s="12"/>
-      <c r="G131" s="13"/>
-      <c r="H131" s="13"/>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A132" s="14" t="s">
-        <v>305</v>
-      </c>
-      <c r="B132" s="14" t="s">
-        <v>500</v>
-      </c>
-      <c r="C132" s="14" t="s">
+      <c r="F155" s="14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
         <v>588</v>
       </c>
-      <c r="D132" s="14" t="s">
-        <v>575</v>
-      </c>
-      <c r="E132" s="14" t="s">
-        <v>576</v>
-      </c>
-      <c r="F132" s="12"/>
-      <c r="G132" s="13"/>
-      <c r="H132" s="13"/>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A133" s="14" t="s">
-        <v>306</v>
-      </c>
-      <c r="B133" s="14" t="s">
-        <v>501</v>
-      </c>
-      <c r="C133" s="14" t="s">
-        <v>348</v>
-      </c>
-      <c r="D133" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="E133" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="F133" s="12"/>
-      <c r="G133" s="13"/>
-      <c r="H133" s="13"/>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A134" s="14" t="s">
-        <v>307</v>
-      </c>
-      <c r="B134" s="14" t="s">
-        <v>502</v>
-      </c>
-      <c r="C134" s="14" t="s">
-        <v>349</v>
-      </c>
-      <c r="D134" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="E134" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="F134" s="12"/>
-      <c r="G134" s="13"/>
-      <c r="H134" s="13"/>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A135" s="14" t="s">
-        <v>308</v>
-      </c>
-      <c r="B135" s="14" t="s">
-        <v>503</v>
-      </c>
-      <c r="C135" s="14" t="s">
-        <v>350</v>
-      </c>
-      <c r="D135" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="E135" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="F135" s="12"/>
-      <c r="G135" s="13"/>
-      <c r="H135" s="13"/>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A136" s="14" t="s">
-        <v>309</v>
-      </c>
-      <c r="B136" s="14" t="s">
-        <v>504</v>
-      </c>
-      <c r="C136" s="14" t="s">
-        <v>351</v>
-      </c>
-      <c r="D136" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="E136" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="F136" s="12"/>
-      <c r="G136" s="13"/>
-      <c r="H136" s="13"/>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A137" s="14" t="s">
-        <v>310</v>
-      </c>
-      <c r="B137" s="14" t="s">
-        <v>505</v>
-      </c>
-      <c r="C137" s="14" t="s">
-        <v>352</v>
-      </c>
-      <c r="D137" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="E137" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="F137" s="12"/>
-      <c r="G137" s="13"/>
-      <c r="H137" s="13"/>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A138" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="B138" s="14" t="s">
-        <v>506</v>
-      </c>
-      <c r="C138" s="14" t="s">
-        <v>353</v>
-      </c>
-      <c r="D138" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="E138" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="F138" s="12"/>
-      <c r="G138" s="13"/>
-      <c r="H138" s="13"/>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A139" s="14" t="s">
-        <v>312</v>
-      </c>
-      <c r="B139" s="14" t="s">
-        <v>507</v>
-      </c>
-      <c r="C139" s="14" t="s">
-        <v>354</v>
-      </c>
-      <c r="D139" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="E139" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="F139" s="12"/>
-      <c r="G139" s="13"/>
-      <c r="H139" s="13"/>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A140" s="14" t="s">
-        <v>313</v>
-      </c>
-      <c r="B140" s="14" t="s">
-        <v>508</v>
-      </c>
-      <c r="C140" s="14" t="s">
-        <v>355</v>
-      </c>
-      <c r="D140" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="E140" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="F140" s="12"/>
-      <c r="G140" s="13"/>
-      <c r="H140" s="13"/>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A141" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="B141" s="14" t="s">
-        <v>509</v>
-      </c>
-      <c r="C141" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="D141" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="E141" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="F141" s="12"/>
-      <c r="G141" s="13"/>
-      <c r="H141" s="13"/>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A142" s="14" t="s">
-        <v>315</v>
-      </c>
-      <c r="B142" s="14" t="s">
-        <v>510</v>
-      </c>
-      <c r="C142" s="14" t="s">
-        <v>357</v>
-      </c>
-      <c r="D142" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="E142" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="F142" s="12"/>
-      <c r="G142" s="13"/>
-      <c r="H142" s="13"/>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A143" s="14" t="s">
-        <v>316</v>
-      </c>
-      <c r="B143" s="14" t="s">
-        <v>511</v>
-      </c>
-      <c r="C143" s="14" t="s">
-        <v>358</v>
-      </c>
-      <c r="D143" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="E143" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="F143" s="12"/>
-      <c r="G143" s="13"/>
-      <c r="H143" s="13"/>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A144" s="14" t="s">
-        <v>317</v>
-      </c>
-      <c r="B144" s="14" t="s">
-        <v>512</v>
-      </c>
-      <c r="C144" s="14" t="s">
-        <v>359</v>
-      </c>
-      <c r="D144" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="E144" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="F144" s="12"/>
-      <c r="G144" s="13"/>
-      <c r="H144" s="13"/>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A145" s="14" t="s">
-        <v>318</v>
-      </c>
-      <c r="B145" s="14" t="s">
-        <v>513</v>
-      </c>
-      <c r="C145" s="14" t="s">
-        <v>360</v>
-      </c>
-      <c r="D145" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="E145" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="F145" s="12"/>
-      <c r="G145" s="13"/>
-      <c r="H145" s="13"/>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A146" s="14" t="s">
-        <v>319</v>
-      </c>
-      <c r="B146" s="14" t="s">
-        <v>514</v>
-      </c>
-      <c r="C146" s="14" t="s">
-        <v>361</v>
-      </c>
-      <c r="D146" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="E146" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="F146" s="12"/>
-      <c r="G146" s="13"/>
-      <c r="H146" s="13"/>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A147" s="14" t="s">
-        <v>320</v>
-      </c>
-      <c r="B147" s="14" t="s">
-        <v>515</v>
-      </c>
-      <c r="C147" s="14" t="s">
-        <v>320</v>
-      </c>
-      <c r="D147" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="E147" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="F147" s="12"/>
-      <c r="G147" s="13"/>
-      <c r="H147" s="13"/>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A148" s="14" t="s">
-        <v>321</v>
-      </c>
-      <c r="B148" s="14" t="s">
-        <v>516</v>
-      </c>
-      <c r="C148" s="14" t="s">
-        <v>362</v>
-      </c>
-      <c r="D148" s="14" t="s">
-        <v>531</v>
-      </c>
-      <c r="E148" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="F148" s="12"/>
-      <c r="G148" s="13"/>
-      <c r="H148" s="13"/>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A149" s="14" t="s">
-        <v>322</v>
-      </c>
-      <c r="B149" s="14" t="s">
-        <v>517</v>
-      </c>
-      <c r="C149" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="D149" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="E149" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="F149" s="12"/>
-      <c r="G149" s="13"/>
-      <c r="H149" s="13"/>
-    </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A150" s="14" t="s">
-        <v>323</v>
-      </c>
-      <c r="B150" s="14" t="s">
-        <v>518</v>
-      </c>
-      <c r="C150" s="14" t="s">
+      <c r="B156" t="s">
         <v>589</v>
       </c>
-      <c r="D150" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="E150" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="F150" s="12"/>
-      <c r="G150" s="13"/>
-      <c r="H150" s="13"/>
-    </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A151" s="14" t="s">
-        <v>324</v>
-      </c>
-      <c r="B151" s="14" t="s">
-        <v>519</v>
-      </c>
-      <c r="C151" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="D151" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="E151" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="F151" s="12"/>
-      <c r="G151" s="13"/>
-      <c r="H151" s="13"/>
-    </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A152" s="14" t="s">
-        <v>325</v>
-      </c>
-      <c r="B152" s="14" t="s">
-        <v>520</v>
-      </c>
-      <c r="C152" s="14" t="s">
-        <v>365</v>
-      </c>
-      <c r="D152" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="E152" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="F152" s="12"/>
-      <c r="G152" s="13"/>
-      <c r="H152" s="13"/>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A153" s="14" t="s">
-        <v>326</v>
-      </c>
-      <c r="B153" s="14" t="s">
-        <v>521</v>
-      </c>
-      <c r="C153" s="14" t="s">
-        <v>368</v>
-      </c>
-      <c r="D153" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="E153" s="14" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A154" s="14" t="s">
-        <v>327</v>
-      </c>
-      <c r="B154" s="14" t="s">
-        <v>522</v>
-      </c>
-      <c r="C154" s="14" t="s">
-        <v>366</v>
-      </c>
-      <c r="D154" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="E154" s="14" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A155" s="14" t="s">
-        <v>328</v>
-      </c>
-      <c r="B155" s="14" t="s">
-        <v>523</v>
-      </c>
-      <c r="C155" s="14" t="s">
-        <v>367</v>
-      </c>
-      <c r="D155" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="E155" s="14" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A156" s="11" t="s">
+      <c r="C156" t="s">
         <v>590</v>
       </c>
-      <c r="B156" s="14"/>
-      <c r="C156" s="14"/>
-      <c r="D156" s="14"/>
-      <c r="E156" s="14"/>
-    </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A157" s="14" t="s">
+      <c r="F156" s="14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A157" t="s">
         <v>591</v>
       </c>
-      <c r="B157" s="14" t="s">
+      <c r="B157" t="s">
         <v>592</v>
       </c>
-      <c r="C157" s="14" t="s">
+      <c r="C157" t="s">
         <v>593</v>
       </c>
-      <c r="D157" s="14"/>
-      <c r="E157" s="14"/>
-    </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A158" s="14" t="s">
+      <c r="F157" s="14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A158" t="s">
         <v>594</v>
       </c>
-      <c r="B158" s="14" t="s">
+      <c r="B158" t="s">
         <v>595</v>
       </c>
-      <c r="C158" s="14" t="s">
+      <c r="C158" t="s">
         <v>596</v>
       </c>
-      <c r="D158" s="14"/>
-      <c r="E158" s="14"/>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A159" s="14" t="s">
+      <c r="F158" s="14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A159" t="s">
         <v>597</v>
       </c>
-      <c r="B159" s="14" t="s">
+      <c r="B159" t="s">
         <v>598</v>
       </c>
-      <c r="C159" s="14" t="s">
+      <c r="C159" t="s">
         <v>599</v>
       </c>
-      <c r="D159" s="14"/>
-      <c r="E159" s="14"/>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A160" s="14" t="s">
+      <c r="F159" s="14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A160" t="s">
         <v>600</v>
       </c>
-      <c r="B160" s="14" t="s">
+      <c r="B160" t="s">
         <v>601</v>
       </c>
-      <c r="C160" s="14" t="s">
+      <c r="C160" t="s">
         <v>602</v>
       </c>
-      <c r="D160" s="14"/>
-      <c r="E160" s="14"/>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A161" s="14" t="s">
+      <c r="F160" s="14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A161" t="s">
         <v>603</v>
       </c>
-      <c r="B161" s="14" t="s">
+      <c r="B161" t="s">
         <v>604</v>
       </c>
-      <c r="C161" s="14" t="s">
+      <c r="C161" t="s">
         <v>605</v>
       </c>
-      <c r="D161" s="14"/>
-      <c r="E161" s="14"/>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A162" s="14" t="s">
+      <c r="F161" s="14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A162" t="s">
         <v>606</v>
       </c>
-      <c r="B162" s="14" t="s">
+      <c r="B162" t="s">
         <v>607</v>
       </c>
-      <c r="C162" s="14" t="s">
+      <c r="C162" t="s">
         <v>608</v>
       </c>
-      <c r="D162" s="14"/>
-      <c r="E162" s="14"/>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A163" s="14" t="s">
+      <c r="F162" s="14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
         <v>609</v>
       </c>
-      <c r="B163" s="14" t="s">
+      <c r="B163" t="s">
         <v>610</v>
       </c>
-      <c r="C163" s="14" t="s">
+      <c r="C163" t="s">
         <v>611</v>
       </c>
-      <c r="D163" s="14"/>
-      <c r="E163" s="14"/>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A164" s="14" t="s">
+      <c r="F163" s="14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
         <v>612</v>
       </c>
-      <c r="B164" s="14" t="s">
+      <c r="B164" t="s">
         <v>613</v>
       </c>
-      <c r="C164" s="14" t="s">
+      <c r="C164" t="s">
         <v>614</v>
       </c>
-      <c r="D164" s="14"/>
-      <c r="E164" s="14"/>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A165" s="14" t="s">
+      <c r="F164" s="14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
         <v>615</v>
       </c>
-      <c r="B165" s="14" t="s">
+      <c r="B165" t="s">
         <v>616</v>
       </c>
-      <c r="C165" s="14" t="s">
+      <c r="C165" t="s">
         <v>617</v>
       </c>
-      <c r="D165" s="14"/>
-      <c r="E165" s="14"/>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A166" s="14" t="s">
+      <c r="F165" s="14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A166" t="s">
         <v>618</v>
       </c>
-      <c r="B166" s="14" t="s">
+      <c r="B166" t="s">
         <v>619</v>
       </c>
-      <c r="C166" s="14" t="s">
+      <c r="C166" t="s">
         <v>620</v>
       </c>
-      <c r="D166" s="14"/>
-      <c r="E166" s="14"/>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A167" s="14" t="s">
+      <c r="F166" s="14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A167" t="s">
         <v>621</v>
       </c>
-      <c r="B167" s="14" t="s">
+      <c r="B167" t="s">
         <v>622</v>
       </c>
-      <c r="C167" s="14" t="s">
+      <c r="C167" t="s">
         <v>623</v>
       </c>
-      <c r="D167" s="14"/>
-      <c r="E167" s="14"/>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A168" s="14" t="s">
+      <c r="F167" s="14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A168" t="s">
         <v>624</v>
       </c>
-      <c r="B168" s="14" t="s">
+      <c r="B168" t="s">
         <v>625</v>
       </c>
-      <c r="C168" s="14" t="s">
+      <c r="C168" t="s">
         <v>626</v>
       </c>
-      <c r="D168" s="14"/>
-      <c r="E168" s="14"/>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A169" s="14" t="s">
-        <v>627</v>
-      </c>
-      <c r="B169" s="14" t="s">
-        <v>628</v>
-      </c>
-      <c r="C169" s="14" t="s">
-        <v>629</v>
-      </c>
-      <c r="D169" s="14"/>
-      <c r="E169" s="14"/>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A170" s="14" t="s">
-        <v>630</v>
-      </c>
-      <c r="B170" s="14" t="s">
-        <v>631</v>
-      </c>
-      <c r="C170" s="14" t="s">
-        <v>632</v>
-      </c>
-      <c r="D170" s="14"/>
-      <c r="E170" s="14"/>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A171" s="14" t="s">
-        <v>633</v>
-      </c>
-      <c r="B171" s="14" t="s">
-        <v>634</v>
-      </c>
-      <c r="C171" s="14" t="s">
-        <v>635</v>
-      </c>
-      <c r="D171" s="14"/>
-      <c r="E171" s="14"/>
+      <c r="F168" s="14" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Features description LendingClub.xlsx
+++ b/data/Features description LendingClub.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10503"/>
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oskarklima/Documents/Oskar/Škola/Bakalářka/Praktická část/Github/bachelor_thesis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF9879F3-8987-BD46-A44D-3315644469AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CDB6338-578B-4F47-9568-F5766EE60AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="630">
   <si>
     <t>id</t>
   </si>
@@ -716,9 +716,6 @@
   </si>
   <si>
     <t>initialListStatus</t>
-  </si>
-  <si>
-    <t>total_rev_hi_lim  </t>
   </si>
   <si>
     <t>Interest Rate on the loan</t>
@@ -1736,9 +1733,6 @@
     <t>Odstraněno (text a duplicita s proměnnou purpose)</t>
   </si>
   <si>
-    <t>Odstarněno (939 kategorií a odpovídá addr_state)</t>
-  </si>
-  <si>
     <t>Dropped (939 categories and corresponding to addr_state)</t>
   </si>
   <si>
@@ -1754,12 +1748,6 @@
     <t>Dropped (constant value)</t>
   </si>
   <si>
-    <t>Odstraněno - spojeno pro spojené žádosti a odstarněno</t>
-  </si>
-  <si>
-    <t>Dropped - connected for joint apliccations and dropped</t>
-  </si>
-  <si>
     <t>Sum of revolving credit balance of the co-borrowers, net of duplicate balances</t>
   </si>
   <si>
@@ -1925,9 +1913,6 @@
     <t>Měsíce z term</t>
   </si>
   <si>
-    <t>Number of months extracted from the termfeature</t>
-  </si>
-  <si>
     <t>Zdroj - Source: https://github.com/bacover/Capstone-LendingClub/blob/main/LCDataDictionary.xlsx</t>
   </si>
   <si>
@@ -1938,6 +1923,18 @@
   </si>
   <si>
     <t>Dropped (text and duplicate of purpose variable)</t>
+  </si>
+  <si>
+    <t>Odstraněno (939 kategorií a odpovídá addr_state)</t>
+  </si>
+  <si>
+    <t>Odstraněno - spojeno pro spojené žádosti a odstraněno</t>
+  </si>
+  <si>
+    <t>Dropped - connected for joint applications and dropped</t>
+  </si>
+  <si>
+    <t>Number of months extracted from the term feature</t>
   </si>
 </sst>
 </file>
@@ -2889,12 +2886,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EE29E4E4-43B3-174E-8F3B-5AB70E293FBE}" name="Table2" displayName="Table2" ref="A3:F168" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
   <autoFilter ref="A3:F168" xr:uid="{EE29E4E4-43B3-174E-8F3B-5AB70E293FBE}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{F3E53C65-DD0F-CB46-8219-E6650EF65E70}" name="Sloupec" dataDxfId="11" totalsRowDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{3A02C682-E8DB-384F-9ED3-84A3FF96F6A6}" name="Český popis" dataDxfId="9" totalsRowDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{5042C38D-E653-3547-BE39-3134ABFE15C8}" name="Anglický popis" dataDxfId="7" totalsRowDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{004D6F80-4F83-9F4D-BBA3-AD6ACAAE4B8F}" name="Zpracování" dataDxfId="5" totalsRowDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{FC8D4EE5-BDDE-1F42-89F2-9A6E869944FE}" name="Processing" dataDxfId="3" totalsRowDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{E8212FED-A26F-EB4D-B375-A7BBE53E82D6}" name="Využito/Used" dataDxfId="1" totalsRowDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{F3E53C65-DD0F-CB46-8219-E6650EF65E70}" name="Sloupec" dataDxfId="10" totalsRowDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{3A02C682-E8DB-384F-9ED3-84A3FF96F6A6}" name="Český popis" dataDxfId="8" totalsRowDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{5042C38D-E653-3547-BE39-3134ABFE15C8}" name="Anglický popis" dataDxfId="6" totalsRowDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{004D6F80-4F83-9F4D-BBA3-AD6ACAAE4B8F}" name="Zpracování" dataDxfId="4" totalsRowDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{FC8D4EE5-BDDE-1F42-89F2-9A6E869944FE}" name="Processing" dataDxfId="2" totalsRowDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{E8212FED-A26F-EB4D-B375-A7BBE53E82D6}" name="Využito/Used" dataDxfId="0" totalsRowDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3200,7 +3197,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="F1" s="12"/>
       <c r="G1" s="12"/>
@@ -3211,22 +3208,22 @@
     </row>
     <row r="3" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="D3" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>370</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>372</v>
-      </c>
       <c r="E3" s="11" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="G3" s="13"/>
     </row>
@@ -3235,16 +3232,16 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C4" t="s">
         <v>66</v>
       </c>
       <c r="D4" t="s">
+        <v>538</v>
+      </c>
+      <c r="E4" t="s">
         <v>539</v>
-      </c>
-      <c r="E4" t="s">
-        <v>540</v>
       </c>
       <c r="F4" s="14" t="b">
         <v>0</v>
@@ -3256,16 +3253,16 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C5" t="s">
         <v>72</v>
       </c>
       <c r="D5" t="s">
+        <v>540</v>
+      </c>
+      <c r="E5" t="s">
         <v>541</v>
-      </c>
-      <c r="E5" t="s">
-        <v>542</v>
       </c>
       <c r="F5" s="14" t="b">
         <v>0</v>
@@ -3277,16 +3274,16 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C6" t="s">
         <v>71</v>
       </c>
       <c r="D6" t="s">
+        <v>524</v>
+      </c>
+      <c r="E6" t="s">
         <v>525</v>
-      </c>
-      <c r="E6" t="s">
-        <v>526</v>
       </c>
       <c r="F6" s="14" t="b">
         <v>1</v>
@@ -3298,16 +3295,16 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D7" t="s">
+        <v>542</v>
+      </c>
+      <c r="E7" t="s">
         <v>543</v>
-      </c>
-      <c r="E7" t="s">
-        <v>544</v>
       </c>
       <c r="F7" s="14" t="b">
         <v>0</v>
@@ -3319,16 +3316,16 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D8" t="s">
+        <v>544</v>
+      </c>
+      <c r="E8" t="s">
         <v>545</v>
-      </c>
-      <c r="E8" t="s">
-        <v>546</v>
       </c>
       <c r="F8" s="14" t="b">
         <v>0</v>
@@ -3340,16 +3337,16 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C9" t="s">
         <v>86</v>
       </c>
       <c r="D9" t="s">
+        <v>546</v>
+      </c>
+      <c r="E9" t="s">
         <v>547</v>
-      </c>
-      <c r="E9" t="s">
-        <v>548</v>
       </c>
       <c r="F9" s="14" t="b">
         <v>0</v>
@@ -3361,16 +3358,16 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C10" t="s">
         <v>92</v>
       </c>
       <c r="D10" t="s">
+        <v>524</v>
+      </c>
+      <c r="E10" t="s">
         <v>525</v>
-      </c>
-      <c r="E10" t="s">
-        <v>526</v>
       </c>
       <c r="F10" s="14" t="b">
         <v>1</v>
@@ -3382,16 +3379,16 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C11" t="s">
         <v>69</v>
       </c>
       <c r="D11" t="s">
+        <v>524</v>
+      </c>
+      <c r="E11" t="s">
         <v>525</v>
-      </c>
-      <c r="E11" t="s">
-        <v>526</v>
       </c>
       <c r="F11" s="14" t="b">
         <v>1</v>
@@ -3403,16 +3400,16 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C12" t="s">
         <v>64</v>
       </c>
       <c r="D12" t="s">
+        <v>548</v>
+      </c>
+      <c r="E12" t="s">
         <v>549</v>
-      </c>
-      <c r="E12" t="s">
-        <v>550</v>
       </c>
       <c r="F12" s="14" t="b">
         <v>0</v>
@@ -3424,16 +3421,16 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C13" t="s">
         <v>85</v>
       </c>
       <c r="D13" t="s">
+        <v>526</v>
+      </c>
+      <c r="E13" t="s">
         <v>527</v>
-      </c>
-      <c r="E13" t="s">
-        <v>528</v>
       </c>
       <c r="F13" s="14" t="b">
         <v>1</v>
@@ -3445,16 +3442,16 @@
         <v>173</v>
       </c>
       <c r="B14" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C14" t="s">
         <v>174</v>
       </c>
       <c r="D14" t="s">
+        <v>528</v>
+      </c>
+      <c r="E14" t="s">
         <v>529</v>
-      </c>
-      <c r="E14" t="s">
-        <v>530</v>
       </c>
       <c r="F14" s="14" t="b">
         <v>0</v>
@@ -3466,16 +3463,16 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C15" t="s">
         <v>185</v>
       </c>
       <c r="D15" t="s">
+        <v>526</v>
+      </c>
+      <c r="E15" t="s">
         <v>527</v>
-      </c>
-      <c r="E15" t="s">
-        <v>528</v>
       </c>
       <c r="F15" s="14" t="b">
         <v>1</v>
@@ -3487,16 +3484,16 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C16" t="s">
         <v>65</v>
       </c>
       <c r="D16" t="s">
+        <v>550</v>
+      </c>
+      <c r="E16" t="s">
         <v>551</v>
-      </c>
-      <c r="E16" t="s">
-        <v>552</v>
       </c>
       <c r="F16" s="14" t="b">
         <v>1</v>
@@ -3508,16 +3505,16 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C17" t="s">
         <v>52</v>
       </c>
       <c r="D17" t="s">
+        <v>524</v>
+      </c>
+      <c r="E17" t="s">
         <v>525</v>
-      </c>
-      <c r="E17" t="s">
-        <v>526</v>
       </c>
       <c r="F17" s="14" t="b">
         <v>1</v>
@@ -3526,19 +3523,19 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B18" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C18" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D18" t="s">
+        <v>530</v>
+      </c>
+      <c r="E18" t="s">
         <v>531</v>
-      </c>
-      <c r="E18" t="s">
-        <v>532</v>
       </c>
       <c r="F18" s="14" t="b">
         <v>1</v>
@@ -3550,19 +3547,19 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C19" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D19" t="s">
+        <v>552</v>
+      </c>
+      <c r="E19" t="s">
         <v>553</v>
       </c>
-      <c r="E19" t="s">
-        <v>554</v>
-      </c>
       <c r="F19" s="14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" s="13"/>
     </row>
@@ -3571,16 +3568,16 @@
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C20" t="s">
         <v>95</v>
       </c>
       <c r="D20" t="s">
+        <v>554</v>
+      </c>
+      <c r="E20" t="s">
         <v>555</v>
-      </c>
-      <c r="E20" t="s">
-        <v>556</v>
       </c>
       <c r="F20" s="14" t="b">
         <v>0</v>
@@ -3592,16 +3589,16 @@
         <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C21" t="s">
         <v>98</v>
       </c>
       <c r="D21" t="s">
+        <v>556</v>
+      </c>
+      <c r="E21" t="s">
         <v>557</v>
-      </c>
-      <c r="E21" t="s">
-        <v>558</v>
       </c>
       <c r="F21" s="14" t="b">
         <v>0</v>
@@ -3613,16 +3610,16 @@
         <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C22" t="s">
         <v>91</v>
       </c>
       <c r="D22" t="s">
+        <v>532</v>
+      </c>
+      <c r="E22" t="s">
         <v>533</v>
-      </c>
-      <c r="E22" t="s">
-        <v>534</v>
       </c>
       <c r="F22" s="14" t="b">
         <v>0</v>
@@ -3634,16 +3631,16 @@
         <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C23" t="s">
         <v>58</v>
       </c>
       <c r="D23" t="s">
+        <v>558</v>
+      </c>
+      <c r="E23" t="s">
         <v>559</v>
-      </c>
-      <c r="E23" t="s">
-        <v>560</v>
       </c>
       <c r="F23" s="14" t="b">
         <v>0</v>
@@ -3655,16 +3652,16 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C24" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D24" t="s">
+        <v>530</v>
+      </c>
+      <c r="E24" t="s">
         <v>531</v>
-      </c>
-      <c r="E24" t="s">
-        <v>532</v>
       </c>
       <c r="F24" s="14" t="b">
         <v>1</v>
@@ -3676,16 +3673,16 @@
         <v>20</v>
       </c>
       <c r="B25" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C25" t="s">
         <v>87</v>
       </c>
       <c r="D25" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E25" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="F25" s="14" t="b">
         <v>0</v>
@@ -3694,19 +3691,19 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B26" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C26" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D26" t="s">
-        <v>563</v>
+        <v>626</v>
       </c>
       <c r="E26" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="F26" s="14" t="b">
         <v>0</v>
@@ -3718,16 +3715,16 @@
         <v>21</v>
       </c>
       <c r="B27" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C27" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D27" t="s">
+        <v>530</v>
+      </c>
+      <c r="E27" t="s">
         <v>531</v>
-      </c>
-      <c r="E27" t="s">
-        <v>532</v>
       </c>
       <c r="F27" s="14" t="b">
         <v>1</v>
@@ -3739,16 +3736,16 @@
         <v>22</v>
       </c>
       <c r="B28" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C28" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D28" t="s">
+        <v>524</v>
+      </c>
+      <c r="E28" t="s">
         <v>525</v>
-      </c>
-      <c r="E28" t="s">
-        <v>526</v>
       </c>
       <c r="F28" s="14" t="b">
         <v>1</v>
@@ -3760,16 +3757,16 @@
         <v>23</v>
       </c>
       <c r="B29" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C29" t="s">
         <v>56</v>
       </c>
       <c r="D29" t="s">
+        <v>524</v>
+      </c>
+      <c r="E29" t="s">
         <v>525</v>
-      </c>
-      <c r="E29" t="s">
-        <v>526</v>
       </c>
       <c r="F29" s="14" t="b">
         <v>1</v>
@@ -3781,19 +3778,19 @@
         <v>24</v>
       </c>
       <c r="B30" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C30" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D30" t="s">
+        <v>534</v>
+      </c>
+      <c r="E30" t="s">
         <v>535</v>
       </c>
-      <c r="E30" t="s">
-        <v>536</v>
-      </c>
       <c r="F30" s="14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" s="13"/>
     </row>
@@ -3802,16 +3799,16 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C31" t="s">
         <v>63</v>
       </c>
       <c r="D31" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E31" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="F31" s="14" t="b">
         <v>0</v>
@@ -3823,16 +3820,16 @@
         <v>26</v>
       </c>
       <c r="B32" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C32" t="s">
         <v>62</v>
       </c>
       <c r="D32" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E32" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="F32" s="14" t="b">
         <v>0</v>
@@ -3844,16 +3841,16 @@
         <v>27</v>
       </c>
       <c r="B33" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C33" t="s">
         <v>68</v>
       </c>
       <c r="D33" t="s">
+        <v>524</v>
+      </c>
+      <c r="E33" t="s">
         <v>525</v>
-      </c>
-      <c r="E33" t="s">
-        <v>526</v>
       </c>
       <c r="F33" s="14" t="b">
         <v>1</v>
@@ -3865,16 +3862,16 @@
         <v>28</v>
       </c>
       <c r="B34" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C34" t="s">
         <v>74</v>
       </c>
       <c r="D34" t="s">
+        <v>524</v>
+      </c>
+      <c r="E34" t="s">
         <v>525</v>
-      </c>
-      <c r="E34" t="s">
-        <v>526</v>
       </c>
       <c r="F34" s="14" t="b">
         <v>1</v>
@@ -3886,16 +3883,16 @@
         <v>29</v>
       </c>
       <c r="B35" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C35" t="s">
         <v>75</v>
       </c>
       <c r="D35" t="s">
+        <v>524</v>
+      </c>
+      <c r="E35" t="s">
         <v>525</v>
-      </c>
-      <c r="E35" t="s">
-        <v>526</v>
       </c>
       <c r="F35" s="14" t="b">
         <v>1</v>
@@ -3907,16 +3904,16 @@
         <v>30</v>
       </c>
       <c r="B36" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C36" t="s">
         <v>80</v>
       </c>
       <c r="D36" t="s">
+        <v>524</v>
+      </c>
+      <c r="E36" t="s">
         <v>525</v>
-      </c>
-      <c r="E36" t="s">
-        <v>526</v>
       </c>
       <c r="F36" s="14" t="b">
         <v>1</v>
@@ -3928,16 +3925,16 @@
         <v>31</v>
       </c>
       <c r="B37" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C37" t="s">
         <v>82</v>
       </c>
       <c r="D37" t="s">
+        <v>524</v>
+      </c>
+      <c r="E37" t="s">
         <v>525</v>
-      </c>
-      <c r="E37" t="s">
-        <v>526</v>
       </c>
       <c r="F37" s="14" t="b">
         <v>1</v>
@@ -3949,16 +3946,16 @@
         <v>32</v>
       </c>
       <c r="B38" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C38" t="s">
         <v>83</v>
       </c>
       <c r="D38" t="s">
+        <v>524</v>
+      </c>
+      <c r="E38" t="s">
         <v>525</v>
-      </c>
-      <c r="E38" t="s">
-        <v>526</v>
       </c>
       <c r="F38" s="14" t="b">
         <v>1</v>
@@ -3970,16 +3967,16 @@
         <v>33</v>
       </c>
       <c r="B39" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C39" t="s">
         <v>84</v>
       </c>
       <c r="D39" t="s">
+        <v>524</v>
+      </c>
+      <c r="E39" t="s">
         <v>525</v>
-      </c>
-      <c r="E39" t="s">
-        <v>526</v>
       </c>
       <c r="F39" s="14" t="b">
         <v>1</v>
@@ -3991,16 +3988,16 @@
         <v>34</v>
       </c>
       <c r="B40" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C40" t="s">
         <v>88</v>
       </c>
       <c r="D40" t="s">
+        <v>524</v>
+      </c>
+      <c r="E40" t="s">
         <v>525</v>
-      </c>
-      <c r="E40" t="s">
-        <v>526</v>
       </c>
       <c r="F40" s="14" t="b">
         <v>1</v>
@@ -4012,16 +4009,16 @@
         <v>35</v>
       </c>
       <c r="B41" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C41" t="s">
         <v>67</v>
       </c>
       <c r="D41" t="s">
+        <v>530</v>
+      </c>
+      <c r="E41" t="s">
         <v>531</v>
-      </c>
-      <c r="E41" t="s">
-        <v>532</v>
       </c>
       <c r="F41" s="14" t="b">
         <v>1</v>
@@ -4033,16 +4030,16 @@
         <v>36</v>
       </c>
       <c r="B42" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C42" t="s">
         <v>96</v>
       </c>
       <c r="D42" t="s">
+        <v>536</v>
+      </c>
+      <c r="E42" t="s">
         <v>537</v>
-      </c>
-      <c r="E42" t="s">
-        <v>538</v>
       </c>
       <c r="F42" s="14" t="b">
         <v>0</v>
@@ -4054,16 +4051,16 @@
         <v>37</v>
       </c>
       <c r="B43" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C43" t="s">
         <v>97</v>
       </c>
       <c r="D43" t="s">
+        <v>536</v>
+      </c>
+      <c r="E43" t="s">
         <v>537</v>
-      </c>
-      <c r="E43" t="s">
-        <v>538</v>
       </c>
       <c r="F43" s="14" t="b">
         <v>0</v>
@@ -4075,16 +4072,16 @@
         <v>38</v>
       </c>
       <c r="B44" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C44" t="s">
         <v>99</v>
       </c>
       <c r="D44" t="s">
+        <v>536</v>
+      </c>
+      <c r="E44" t="s">
         <v>537</v>
-      </c>
-      <c r="E44" t="s">
-        <v>538</v>
       </c>
       <c r="F44" s="14" t="b">
         <v>0</v>
@@ -4096,16 +4093,16 @@
         <v>39</v>
       </c>
       <c r="B45" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C45" t="s">
         <v>100</v>
       </c>
       <c r="D45" t="s">
+        <v>536</v>
+      </c>
+      <c r="E45" t="s">
         <v>537</v>
-      </c>
-      <c r="E45" t="s">
-        <v>538</v>
       </c>
       <c r="F45" s="14" t="b">
         <v>0</v>
@@ -4117,16 +4114,16 @@
         <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C46" t="s">
         <v>103</v>
       </c>
       <c r="D46" t="s">
+        <v>536</v>
+      </c>
+      <c r="E46" t="s">
         <v>537</v>
-      </c>
-      <c r="E46" t="s">
-        <v>538</v>
       </c>
       <c r="F46" s="14" t="b">
         <v>0</v>
@@ -4138,16 +4135,16 @@
         <v>41</v>
       </c>
       <c r="B47" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C47" t="s">
         <v>102</v>
       </c>
       <c r="D47" t="s">
+        <v>536</v>
+      </c>
+      <c r="E47" t="s">
         <v>537</v>
-      </c>
-      <c r="E47" t="s">
-        <v>538</v>
       </c>
       <c r="F47" s="14" t="b">
         <v>0</v>
@@ -4159,16 +4156,16 @@
         <v>42</v>
       </c>
       <c r="B48" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C48" t="s">
         <v>101</v>
       </c>
       <c r="D48" t="s">
+        <v>536</v>
+      </c>
+      <c r="E48" t="s">
         <v>537</v>
-      </c>
-      <c r="E48" t="s">
-        <v>538</v>
       </c>
       <c r="F48" s="14" t="b">
         <v>0</v>
@@ -4177,19 +4174,19 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B49" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C49" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D49" t="s">
+        <v>536</v>
+      </c>
+      <c r="E49" t="s">
         <v>537</v>
-      </c>
-      <c r="E49" t="s">
-        <v>538</v>
       </c>
       <c r="F49" s="14" t="b">
         <v>0</v>
@@ -4198,19 +4195,19 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B50" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C50" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D50" t="s">
+        <v>536</v>
+      </c>
+      <c r="E50" t="s">
         <v>537</v>
-      </c>
-      <c r="E50" t="s">
-        <v>538</v>
       </c>
       <c r="F50" s="14" t="b">
         <v>0</v>
@@ -4222,16 +4219,16 @@
         <v>43</v>
       </c>
       <c r="B51" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C51" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D51" t="s">
+        <v>536</v>
+      </c>
+      <c r="E51" t="s">
         <v>537</v>
-      </c>
-      <c r="E51" t="s">
-        <v>538</v>
       </c>
       <c r="F51" s="14" t="b">
         <v>0</v>
@@ -4243,16 +4240,16 @@
         <v>44</v>
       </c>
       <c r="B52" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C52" t="s">
         <v>104</v>
       </c>
       <c r="D52" t="s">
+        <v>536</v>
+      </c>
+      <c r="E52" t="s">
         <v>537</v>
-      </c>
-      <c r="E52" t="s">
-        <v>538</v>
       </c>
       <c r="F52" s="14" t="b">
         <v>0</v>
@@ -4264,16 +4261,16 @@
         <v>45</v>
       </c>
       <c r="B53" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C53" t="s">
         <v>105</v>
       </c>
       <c r="D53" t="s">
+        <v>536</v>
+      </c>
+      <c r="E53" t="s">
         <v>537</v>
-      </c>
-      <c r="E53" t="s">
-        <v>538</v>
       </c>
       <c r="F53" s="14" t="b">
         <v>0</v>
@@ -4285,16 +4282,16 @@
         <v>46</v>
       </c>
       <c r="B54" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C54" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D54" t="s">
+        <v>536</v>
+      </c>
+      <c r="E54" t="s">
         <v>537</v>
-      </c>
-      <c r="E54" t="s">
-        <v>538</v>
       </c>
       <c r="F54" s="14" t="b">
         <v>0</v>
@@ -4306,16 +4303,16 @@
         <v>47</v>
       </c>
       <c r="B55" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C55" t="s">
         <v>93</v>
       </c>
       <c r="D55" t="s">
+        <v>536</v>
+      </c>
+      <c r="E55" t="s">
         <v>537</v>
-      </c>
-      <c r="E55" t="s">
-        <v>538</v>
       </c>
       <c r="F55" s="14" t="b">
         <v>0</v>
@@ -4327,16 +4324,16 @@
         <v>48</v>
       </c>
       <c r="B56" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C56" t="s">
         <v>94</v>
       </c>
       <c r="D56" t="s">
+        <v>536</v>
+      </c>
+      <c r="E56" t="s">
         <v>537</v>
-      </c>
-      <c r="E56" t="s">
-        <v>538</v>
       </c>
       <c r="F56" s="14" t="b">
         <v>0</v>
@@ -4348,16 +4345,16 @@
         <v>113</v>
       </c>
       <c r="B57" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C57" t="s">
         <v>138</v>
       </c>
       <c r="D57" t="s">
+        <v>524</v>
+      </c>
+      <c r="E57" t="s">
         <v>525</v>
-      </c>
-      <c r="E57" t="s">
-        <v>526</v>
       </c>
       <c r="F57" s="14" t="b">
         <v>1</v>
@@ -4369,16 +4366,16 @@
         <v>115</v>
       </c>
       <c r="B58" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C58" t="s">
         <v>143</v>
       </c>
       <c r="D58" t="s">
+        <v>524</v>
+      </c>
+      <c r="E58" t="s">
         <v>525</v>
-      </c>
-      <c r="E58" t="s">
-        <v>526</v>
       </c>
       <c r="F58" s="14" t="b">
         <v>1</v>
@@ -4390,16 +4387,16 @@
         <v>136</v>
       </c>
       <c r="B59" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C59" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="D59" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E59" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F59" s="14" t="b">
         <v>0</v>
@@ -4408,19 +4405,19 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B60" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C60" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D60" t="s">
+        <v>530</v>
+      </c>
+      <c r="E60" t="s">
         <v>531</v>
-      </c>
-      <c r="E60" t="s">
-        <v>532</v>
       </c>
       <c r="F60" s="14" t="b">
         <v>1</v>
@@ -4429,19 +4426,19 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B61" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C61" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D61" t="s">
-        <v>569</v>
+        <v>627</v>
       </c>
       <c r="E61" t="s">
-        <v>570</v>
+        <v>628</v>
       </c>
       <c r="F61" s="14" t="b">
         <v>0</v>
@@ -4450,19 +4447,19 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B62" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C62" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D62" t="s">
-        <v>569</v>
+        <v>627</v>
       </c>
       <c r="E62" t="s">
-        <v>570</v>
+        <v>628</v>
       </c>
       <c r="F62" s="14" t="b">
         <v>0</v>
@@ -4471,19 +4468,19 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B63" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C63" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D63" t="s">
-        <v>569</v>
+        <v>627</v>
       </c>
       <c r="E63" t="s">
-        <v>570</v>
+        <v>628</v>
       </c>
       <c r="F63" s="14" t="b">
         <v>0</v>
@@ -4492,19 +4489,19 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B64" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C64" t="s">
         <v>50</v>
       </c>
       <c r="D64" t="s">
+        <v>524</v>
+      </c>
+      <c r="E64" t="s">
         <v>525</v>
-      </c>
-      <c r="E64" t="s">
-        <v>526</v>
       </c>
       <c r="F64" s="14" t="b">
         <v>1</v>
@@ -4516,16 +4513,16 @@
         <v>135</v>
       </c>
       <c r="B65" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C65" t="s">
         <v>163</v>
       </c>
       <c r="D65" t="s">
+        <v>524</v>
+      </c>
+      <c r="E65" t="s">
         <v>525</v>
-      </c>
-      <c r="E65" t="s">
-        <v>526</v>
       </c>
       <c r="F65" s="14" t="b">
         <v>1</v>
@@ -4537,16 +4534,16 @@
         <v>120</v>
       </c>
       <c r="B66" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C66" t="s">
         <v>162</v>
       </c>
       <c r="D66" t="s">
+        <v>524</v>
+      </c>
+      <c r="E66" t="s">
         <v>525</v>
-      </c>
-      <c r="E66" t="s">
-        <v>526</v>
       </c>
       <c r="F66" s="14" t="b">
         <v>1</v>
@@ -4555,19 +4552,19 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B67" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C67" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D67" t="s">
+        <v>524</v>
+      </c>
+      <c r="E67" t="s">
         <v>525</v>
-      </c>
-      <c r="E67" t="s">
-        <v>526</v>
       </c>
       <c r="F67" s="14" t="b">
         <v>1</v>
@@ -4576,19 +4573,19 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B68" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C68" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D68" t="s">
+        <v>524</v>
+      </c>
+      <c r="E68" t="s">
         <v>525</v>
-      </c>
-      <c r="E68" t="s">
-        <v>526</v>
       </c>
       <c r="F68" s="14" t="b">
         <v>1</v>
@@ -4597,19 +4594,19 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B69" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C69" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D69" t="s">
+        <v>524</v>
+      </c>
+      <c r="E69" t="s">
         <v>525</v>
-      </c>
-      <c r="E69" t="s">
-        <v>526</v>
       </c>
       <c r="F69" s="14" t="b">
         <v>1</v>
@@ -4618,19 +4615,19 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B70" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C70" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D70" t="s">
+        <v>524</v>
+      </c>
+      <c r="E70" t="s">
         <v>525</v>
-      </c>
-      <c r="E70" t="s">
-        <v>526</v>
       </c>
       <c r="F70" s="14" t="b">
         <v>1</v>
@@ -4639,19 +4636,19 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B71" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C71" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D71" t="s">
+        <v>524</v>
+      </c>
+      <c r="E71" t="s">
         <v>525</v>
-      </c>
-      <c r="E71" t="s">
-        <v>526</v>
       </c>
       <c r="F71" s="14" t="b">
         <v>1</v>
@@ -4660,19 +4657,19 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B72" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C72" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D72" t="s">
+        <v>524</v>
+      </c>
+      <c r="E72" t="s">
         <v>525</v>
-      </c>
-      <c r="E72" t="s">
-        <v>526</v>
       </c>
       <c r="F72" s="14" t="b">
         <v>1</v>
@@ -4681,19 +4678,19 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B73" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C73" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D73" t="s">
+        <v>524</v>
+      </c>
+      <c r="E73" t="s">
         <v>525</v>
-      </c>
-      <c r="E73" t="s">
-        <v>526</v>
       </c>
       <c r="F73" s="14" t="b">
         <v>1</v>
@@ -4702,19 +4699,19 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B74" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C74" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D74" t="s">
+        <v>524</v>
+      </c>
+      <c r="E74" t="s">
         <v>525</v>
-      </c>
-      <c r="E74" t="s">
-        <v>526</v>
       </c>
       <c r="F74" s="14" t="b">
         <v>1</v>
@@ -4723,19 +4720,19 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B75" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C75" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D75" t="s">
+        <v>524</v>
+      </c>
+      <c r="E75" t="s">
         <v>525</v>
-      </c>
-      <c r="E75" t="s">
-        <v>526</v>
       </c>
       <c r="F75" s="14" t="b">
         <v>1</v>
@@ -4744,19 +4741,19 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B76" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C76" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D76" t="s">
+        <v>524</v>
+      </c>
+      <c r="E76" t="s">
         <v>525</v>
-      </c>
-      <c r="E76" t="s">
-        <v>526</v>
       </c>
       <c r="F76" s="14" t="b">
         <v>1</v>
@@ -4765,19 +4762,19 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B77" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C77" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D77" t="s">
+        <v>524</v>
+      </c>
+      <c r="E77" t="s">
         <v>525</v>
-      </c>
-      <c r="E77" t="s">
-        <v>526</v>
       </c>
       <c r="F77" s="14" t="b">
         <v>1</v>
@@ -4786,19 +4783,19 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B78" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C78" t="s">
         <v>165</v>
       </c>
       <c r="D78" t="s">
+        <v>524</v>
+      </c>
+      <c r="E78" t="s">
         <v>525</v>
-      </c>
-      <c r="E78" t="s">
-        <v>526</v>
       </c>
       <c r="F78" s="14" t="b">
         <v>1</v>
@@ -4807,19 +4804,19 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B79" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C79" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D79" t="s">
+        <v>524</v>
+      </c>
+      <c r="E79" t="s">
         <v>525</v>
-      </c>
-      <c r="E79" t="s">
-        <v>526</v>
       </c>
       <c r="F79" s="14" t="b">
         <v>1</v>
@@ -4828,19 +4825,19 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B80" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C80" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D80" t="s">
+        <v>524</v>
+      </c>
+      <c r="E80" t="s">
         <v>525</v>
-      </c>
-      <c r="E80" t="s">
-        <v>526</v>
       </c>
       <c r="F80" s="14" t="b">
         <v>1</v>
@@ -4849,19 +4846,19 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B81" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C81" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D81" t="s">
+        <v>524</v>
+      </c>
+      <c r="E81" t="s">
         <v>525</v>
-      </c>
-      <c r="E81" t="s">
-        <v>526</v>
       </c>
       <c r="F81" s="14" t="b">
         <v>1</v>
@@ -4870,19 +4867,19 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B82" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C82" t="s">
         <v>51</v>
       </c>
       <c r="D82" t="s">
+        <v>524</v>
+      </c>
+      <c r="E82" t="s">
         <v>525</v>
-      </c>
-      <c r="E82" t="s">
-        <v>526</v>
       </c>
       <c r="F82" s="14" t="b">
         <v>1</v>
@@ -4894,16 +4891,16 @@
         <v>121</v>
       </c>
       <c r="B83" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C83" t="s">
         <v>166</v>
       </c>
       <c r="D83" t="s">
+        <v>524</v>
+      </c>
+      <c r="E83" t="s">
         <v>525</v>
-      </c>
-      <c r="E83" t="s">
-        <v>526</v>
       </c>
       <c r="F83" s="14" t="b">
         <v>1</v>
@@ -4912,19 +4909,19 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B84" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C84" t="s">
         <v>53</v>
       </c>
       <c r="D84" t="s">
+        <v>524</v>
+      </c>
+      <c r="E84" t="s">
         <v>525</v>
-      </c>
-      <c r="E84" t="s">
-        <v>526</v>
       </c>
       <c r="F84" s="14" t="b">
         <v>1</v>
@@ -4933,19 +4930,19 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B85" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C85" t="s">
         <v>54</v>
       </c>
       <c r="D85" t="s">
+        <v>524</v>
+      </c>
+      <c r="E85" t="s">
         <v>525</v>
-      </c>
-      <c r="E85" t="s">
-        <v>526</v>
       </c>
       <c r="F85" s="14" t="b">
         <v>1</v>
@@ -4957,16 +4954,16 @@
         <v>112</v>
       </c>
       <c r="B86" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C86" t="s">
         <v>137</v>
       </c>
       <c r="D86" t="s">
+        <v>524</v>
+      </c>
+      <c r="E86" t="s">
         <v>525</v>
-      </c>
-      <c r="E86" t="s">
-        <v>526</v>
       </c>
       <c r="F86" s="14" t="b">
         <v>1</v>
@@ -4975,19 +4972,19 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B87" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C87" t="s">
         <v>57</v>
       </c>
       <c r="D87" t="s">
+        <v>524</v>
+      </c>
+      <c r="E87" t="s">
         <v>525</v>
-      </c>
-      <c r="E87" t="s">
-        <v>526</v>
       </c>
       <c r="F87" s="14" t="b">
         <v>1</v>
@@ -4996,19 +4993,19 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B88" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C88" t="s">
         <v>139</v>
       </c>
       <c r="D88" t="s">
+        <v>524</v>
+      </c>
+      <c r="E88" t="s">
         <v>525</v>
-      </c>
-      <c r="E88" t="s">
-        <v>526</v>
       </c>
       <c r="F88" s="14" t="b">
         <v>1</v>
@@ -5020,16 +5017,16 @@
         <v>131</v>
       </c>
       <c r="B89" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C89" t="s">
         <v>140</v>
       </c>
       <c r="D89" t="s">
+        <v>524</v>
+      </c>
+      <c r="E89" t="s">
         <v>525</v>
-      </c>
-      <c r="E89" t="s">
-        <v>526</v>
       </c>
       <c r="F89" s="14" t="b">
         <v>1</v>
@@ -5041,16 +5038,16 @@
         <v>132</v>
       </c>
       <c r="B90" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C90" t="s">
         <v>141</v>
       </c>
       <c r="D90" t="s">
+        <v>524</v>
+      </c>
+      <c r="E90" t="s">
         <v>525</v>
-      </c>
-      <c r="E90" t="s">
-        <v>526</v>
       </c>
       <c r="F90" s="14" t="b">
         <v>1</v>
@@ -5062,16 +5059,16 @@
         <v>118</v>
       </c>
       <c r="B91" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C91" t="s">
         <v>142</v>
       </c>
       <c r="D91" t="s">
+        <v>524</v>
+      </c>
+      <c r="E91" t="s">
         <v>525</v>
-      </c>
-      <c r="E91" t="s">
-        <v>526</v>
       </c>
       <c r="F91" s="14" t="b">
         <v>1</v>
@@ -5080,19 +5077,19 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B92" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C92" t="s">
         <v>73</v>
       </c>
       <c r="D92" t="s">
+        <v>524</v>
+      </c>
+      <c r="E92" t="s">
         <v>525</v>
-      </c>
-      <c r="E92" t="s">
-        <v>526</v>
       </c>
       <c r="F92" s="14" t="b">
         <v>1</v>
@@ -5101,19 +5098,19 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B93" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C93" t="s">
         <v>77</v>
       </c>
       <c r="D93" t="s">
+        <v>524</v>
+      </c>
+      <c r="E93" t="s">
         <v>525</v>
-      </c>
-      <c r="E93" t="s">
-        <v>526</v>
       </c>
       <c r="F93" s="14" t="b">
         <v>1</v>
@@ -5122,19 +5119,19 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B94" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C94" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D94" t="s">
+        <v>524</v>
+      </c>
+      <c r="E94" t="s">
         <v>525</v>
-      </c>
-      <c r="E94" t="s">
-        <v>526</v>
       </c>
       <c r="F94" s="14" t="b">
         <v>1</v>
@@ -5143,19 +5140,19 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B95" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C95" t="s">
         <v>76</v>
       </c>
       <c r="D95" t="s">
+        <v>524</v>
+      </c>
+      <c r="E95" t="s">
         <v>525</v>
-      </c>
-      <c r="E95" t="s">
-        <v>526</v>
       </c>
       <c r="F95" s="14" t="b">
         <v>1</v>
@@ -5164,19 +5161,19 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B96" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C96" t="s">
         <v>79</v>
       </c>
       <c r="D96" t="s">
+        <v>524</v>
+      </c>
+      <c r="E96" t="s">
         <v>525</v>
-      </c>
-      <c r="E96" t="s">
-        <v>526</v>
       </c>
       <c r="F96" s="14" t="b">
         <v>1</v>
@@ -5188,16 +5185,16 @@
         <v>111</v>
       </c>
       <c r="B97" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C97" t="s">
         <v>144</v>
       </c>
       <c r="D97" t="s">
+        <v>524</v>
+      </c>
+      <c r="E97" t="s">
         <v>525</v>
-      </c>
-      <c r="E97" t="s">
-        <v>526</v>
       </c>
       <c r="F97" s="14" t="b">
         <v>1</v>
@@ -5209,16 +5206,16 @@
         <v>123</v>
       </c>
       <c r="B98" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C98" t="s">
         <v>149</v>
       </c>
       <c r="D98" t="s">
+        <v>524</v>
+      </c>
+      <c r="E98" t="s">
         <v>525</v>
-      </c>
-      <c r="E98" t="s">
-        <v>526</v>
       </c>
       <c r="F98" s="14" t="b">
         <v>1</v>
@@ -5230,16 +5227,16 @@
         <v>130</v>
       </c>
       <c r="B99" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C99" t="s">
         <v>155</v>
       </c>
       <c r="D99" t="s">
+        <v>524</v>
+      </c>
+      <c r="E99" t="s">
         <v>525</v>
-      </c>
-      <c r="E99" t="s">
-        <v>526</v>
       </c>
       <c r="F99" s="14" t="b">
         <v>1</v>
@@ -5251,16 +5248,16 @@
         <v>124</v>
       </c>
       <c r="B100" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C100" t="s">
         <v>150</v>
       </c>
       <c r="D100" t="s">
+        <v>524</v>
+      </c>
+      <c r="E100" t="s">
         <v>525</v>
-      </c>
-      <c r="E100" t="s">
-        <v>526</v>
       </c>
       <c r="F100" s="14" t="b">
         <v>1</v>
@@ -5272,16 +5269,16 @@
         <v>122</v>
       </c>
       <c r="B101" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C101" t="s">
         <v>148</v>
       </c>
       <c r="D101" t="s">
+        <v>524</v>
+      </c>
+      <c r="E101" t="s">
         <v>525</v>
-      </c>
-      <c r="E101" t="s">
-        <v>526</v>
       </c>
       <c r="F101" s="14" t="b">
         <v>1</v>
@@ -5293,16 +5290,16 @@
         <v>129</v>
       </c>
       <c r="B102" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C102" t="s">
         <v>154</v>
       </c>
       <c r="D102" t="s">
+        <v>524</v>
+      </c>
+      <c r="E102" t="s">
         <v>525</v>
-      </c>
-      <c r="E102" t="s">
-        <v>526</v>
       </c>
       <c r="F102" s="14" t="b">
         <v>1</v>
@@ -5314,16 +5311,16 @@
         <v>134</v>
       </c>
       <c r="B103" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C103" t="s">
         <v>157</v>
       </c>
       <c r="D103" t="s">
+        <v>524</v>
+      </c>
+      <c r="E103" t="s">
         <v>525</v>
-      </c>
-      <c r="E103" t="s">
-        <v>526</v>
       </c>
       <c r="F103" s="14" t="b">
         <v>1</v>
@@ -5335,16 +5332,16 @@
         <v>109</v>
       </c>
       <c r="B104" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C104" t="s">
         <v>145</v>
       </c>
       <c r="D104" t="s">
+        <v>524</v>
+      </c>
+      <c r="E104" t="s">
         <v>525</v>
-      </c>
-      <c r="E104" t="s">
-        <v>526</v>
       </c>
       <c r="F104" s="14" t="b">
         <v>1</v>
@@ -5356,16 +5353,16 @@
         <v>133</v>
       </c>
       <c r="B105" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C105" t="s">
         <v>156</v>
       </c>
       <c r="D105" t="s">
+        <v>524</v>
+      </c>
+      <c r="E105" t="s">
         <v>525</v>
-      </c>
-      <c r="E105" t="s">
-        <v>526</v>
       </c>
       <c r="F105" s="14" t="b">
         <v>1</v>
@@ -5377,16 +5374,16 @@
         <v>116</v>
       </c>
       <c r="B106" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C106" t="s">
         <v>146</v>
       </c>
       <c r="D106" t="s">
+        <v>524</v>
+      </c>
+      <c r="E106" t="s">
         <v>525</v>
-      </c>
-      <c r="E106" t="s">
-        <v>526</v>
       </c>
       <c r="F106" s="14" t="b">
         <v>1</v>
@@ -5398,16 +5395,16 @@
         <v>128</v>
       </c>
       <c r="B107" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C107" t="s">
         <v>153</v>
       </c>
       <c r="D107" t="s">
+        <v>524</v>
+      </c>
+      <c r="E107" t="s">
         <v>525</v>
-      </c>
-      <c r="E107" t="s">
-        <v>526</v>
       </c>
       <c r="F107" s="14" t="b">
         <v>1</v>
@@ -5419,16 +5416,16 @@
         <v>127</v>
       </c>
       <c r="B108" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C108" t="s">
         <v>152</v>
       </c>
       <c r="D108" t="s">
+        <v>524</v>
+      </c>
+      <c r="E108" t="s">
         <v>525</v>
-      </c>
-      <c r="E108" t="s">
-        <v>526</v>
       </c>
       <c r="F108" s="14" t="b">
         <v>1</v>
@@ -5440,16 +5437,16 @@
         <v>126</v>
       </c>
       <c r="B109" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C109" t="s">
         <v>151</v>
       </c>
       <c r="D109" t="s">
+        <v>524</v>
+      </c>
+      <c r="E109" t="s">
         <v>525</v>
-      </c>
-      <c r="E109" t="s">
-        <v>526</v>
       </c>
       <c r="F109" s="14" t="b">
         <v>1</v>
@@ -5461,16 +5458,16 @@
         <v>117</v>
       </c>
       <c r="B110" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C110" t="s">
         <v>147</v>
       </c>
       <c r="D110" t="s">
+        <v>524</v>
+      </c>
+      <c r="E110" t="s">
         <v>525</v>
-      </c>
-      <c r="E110" t="s">
-        <v>526</v>
       </c>
       <c r="F110" s="14" t="b">
         <v>1</v>
@@ -5482,16 +5479,16 @@
         <v>125</v>
       </c>
       <c r="B111" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C111" t="s">
         <v>158</v>
       </c>
       <c r="D111" t="s">
+        <v>524</v>
+      </c>
+      <c r="E111" t="s">
         <v>525</v>
-      </c>
-      <c r="E111" t="s">
-        <v>526</v>
       </c>
       <c r="F111" s="14" t="b">
         <v>1</v>
@@ -5500,19 +5497,19 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B112" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C112" t="s">
         <v>81</v>
       </c>
       <c r="D112" t="s">
+        <v>524</v>
+      </c>
+      <c r="E112" t="s">
         <v>525</v>
-      </c>
-      <c r="E112" t="s">
-        <v>526</v>
       </c>
       <c r="F112" s="14" t="b">
         <v>1</v>
@@ -5524,16 +5521,16 @@
         <v>110</v>
       </c>
       <c r="B113" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C113" t="s">
         <v>159</v>
       </c>
       <c r="D113" t="s">
+        <v>524</v>
+      </c>
+      <c r="E113" t="s">
         <v>525</v>
-      </c>
-      <c r="E113" t="s">
-        <v>526</v>
       </c>
       <c r="F113" s="14" t="b">
         <v>1</v>
@@ -5545,16 +5542,16 @@
         <v>114</v>
       </c>
       <c r="B114" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C114" t="s">
         <v>160</v>
       </c>
       <c r="D114" t="s">
+        <v>524</v>
+      </c>
+      <c r="E114" t="s">
         <v>525</v>
-      </c>
-      <c r="E114" t="s">
-        <v>526</v>
       </c>
       <c r="F114" s="14" t="b">
         <v>1</v>
@@ -5566,16 +5563,16 @@
         <v>119</v>
       </c>
       <c r="B115" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C115" t="s">
         <v>161</v>
       </c>
       <c r="D115" t="s">
+        <v>524</v>
+      </c>
+      <c r="E115" t="s">
         <v>525</v>
-      </c>
-      <c r="E115" t="s">
-        <v>526</v>
       </c>
       <c r="F115" s="14" t="b">
         <v>1</v>
@@ -5584,19 +5581,19 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B116" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C116" t="s">
         <v>89</v>
       </c>
       <c r="D116" t="s">
+        <v>524</v>
+      </c>
+      <c r="E116" t="s">
         <v>525</v>
-      </c>
-      <c r="E116" t="s">
-        <v>526</v>
       </c>
       <c r="F116" s="14" t="b">
         <v>1</v>
@@ -5605,19 +5602,19 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B117" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C117" t="s">
         <v>90</v>
       </c>
       <c r="D117" t="s">
+        <v>524</v>
+      </c>
+      <c r="E117" t="s">
         <v>525</v>
-      </c>
-      <c r="E117" t="s">
-        <v>526</v>
       </c>
       <c r="F117" s="14" t="b">
         <v>1</v>
@@ -5629,16 +5626,16 @@
         <v>107</v>
       </c>
       <c r="B118" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C118" t="s">
         <v>164</v>
       </c>
       <c r="D118" t="s">
+        <v>524</v>
+      </c>
+      <c r="E118" t="s">
         <v>525</v>
-      </c>
-      <c r="E118" t="s">
-        <v>526</v>
       </c>
       <c r="F118" s="14" t="b">
         <v>1</v>
@@ -5647,19 +5644,19 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B119" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C119" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="D119" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="E119" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F119" s="14" t="b">
         <v>0</v>
@@ -5668,19 +5665,19 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B120" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C120" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="D120" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="E120" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F120" s="14" t="b">
         <v>0</v>
@@ -5689,19 +5686,19 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B121" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C121" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="D121" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="E121" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F121" s="14" t="b">
         <v>0</v>
@@ -5710,19 +5707,19 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B122" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C122" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="D122" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="E122" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F122" s="14" t="b">
         <v>0</v>
@@ -5731,19 +5728,19 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B123" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C123" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="D123" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="E123" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F123" s="14" t="b">
         <v>0</v>
@@ -5752,19 +5749,19 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B124" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C124" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="D124" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="E124" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F124" s="14" t="b">
         <v>0</v>
@@ -5773,19 +5770,19 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B125" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C125" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="D125" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="E125" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F125" s="14" t="b">
         <v>0</v>
@@ -5794,19 +5791,19 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B126" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C126" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="D126" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="E126" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F126" s="14" t="b">
         <v>0</v>
@@ -5815,19 +5812,19 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B127" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C127" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="D127" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="E127" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F127" s="14" t="b">
         <v>0</v>
@@ -5836,19 +5833,19 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B128" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C128" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="D128" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="E128" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F128" s="14" t="b">
         <v>0</v>
@@ -5857,19 +5854,19 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B129" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C129" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="D129" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="E129" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F129" s="14" t="b">
         <v>0</v>
@@ -5878,19 +5875,19 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B130" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C130" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="D130" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="E130" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F130" s="14" t="b">
         <v>0</v>
@@ -5899,19 +5896,19 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B131" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C131" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="D131" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="E131" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F131" s="14" t="b">
         <v>0</v>
@@ -5920,19 +5917,19 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B132" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C132" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D132" t="s">
+        <v>536</v>
+      </c>
+      <c r="E132" t="s">
         <v>537</v>
-      </c>
-      <c r="E132" t="s">
-        <v>538</v>
       </c>
       <c r="F132" s="14" t="b">
         <v>0</v>
@@ -5941,19 +5938,19 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B133" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C133" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D133" t="s">
+        <v>536</v>
+      </c>
+      <c r="E133" t="s">
         <v>537</v>
-      </c>
-      <c r="E133" t="s">
-        <v>538</v>
       </c>
       <c r="F133" s="14" t="b">
         <v>0</v>
@@ -5962,19 +5959,19 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B134" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C134" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D134" t="s">
+        <v>536</v>
+      </c>
+      <c r="E134" t="s">
         <v>537</v>
-      </c>
-      <c r="E134" t="s">
-        <v>538</v>
       </c>
       <c r="F134" s="14" t="b">
         <v>0</v>
@@ -5983,19 +5980,19 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B135" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C135" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D135" t="s">
+        <v>536</v>
+      </c>
+      <c r="E135" t="s">
         <v>537</v>
-      </c>
-      <c r="E135" t="s">
-        <v>538</v>
       </c>
       <c r="F135" s="14" t="b">
         <v>0</v>
@@ -6004,19 +6001,19 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B136" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C136" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D136" t="s">
+        <v>536</v>
+      </c>
+      <c r="E136" t="s">
         <v>537</v>
-      </c>
-      <c r="E136" t="s">
-        <v>538</v>
       </c>
       <c r="F136" s="14" t="b">
         <v>0</v>
@@ -6025,19 +6022,19 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B137" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C137" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D137" t="s">
+        <v>536</v>
+      </c>
+      <c r="E137" t="s">
         <v>537</v>
-      </c>
-      <c r="E137" t="s">
-        <v>538</v>
       </c>
       <c r="F137" s="14" t="b">
         <v>0</v>
@@ -6046,19 +6043,19 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B138" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C138" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D138" t="s">
+        <v>536</v>
+      </c>
+      <c r="E138" t="s">
         <v>537</v>
-      </c>
-      <c r="E138" t="s">
-        <v>538</v>
       </c>
       <c r="F138" s="14" t="b">
         <v>0</v>
@@ -6067,19 +6064,19 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B139" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C139" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D139" t="s">
+        <v>536</v>
+      </c>
+      <c r="E139" t="s">
         <v>537</v>
-      </c>
-      <c r="E139" t="s">
-        <v>538</v>
       </c>
       <c r="F139" s="14" t="b">
         <v>0</v>
@@ -6088,19 +6085,19 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B140" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C140" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D140" t="s">
+        <v>536</v>
+      </c>
+      <c r="E140" t="s">
         <v>537</v>
-      </c>
-      <c r="E140" t="s">
-        <v>538</v>
       </c>
       <c r="F140" s="14" t="b">
         <v>0</v>
@@ -6109,19 +6106,19 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B141" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C141" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D141" t="s">
+        <v>536</v>
+      </c>
+      <c r="E141" t="s">
         <v>537</v>
-      </c>
-      <c r="E141" t="s">
-        <v>538</v>
       </c>
       <c r="F141" s="14" t="b">
         <v>0</v>
@@ -6130,19 +6127,19 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B142" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C142" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D142" t="s">
+        <v>536</v>
+      </c>
+      <c r="E142" t="s">
         <v>537</v>
-      </c>
-      <c r="E142" t="s">
-        <v>538</v>
       </c>
       <c r="F142" s="14" t="b">
         <v>0</v>
@@ -6151,19 +6148,19 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B143" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C143" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D143" t="s">
+        <v>536</v>
+      </c>
+      <c r="E143" t="s">
         <v>537</v>
-      </c>
-      <c r="E143" t="s">
-        <v>538</v>
       </c>
       <c r="F143" s="14" t="b">
         <v>0</v>
@@ -6172,19 +6169,19 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B144" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C144" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D144" t="s">
+        <v>536</v>
+      </c>
+      <c r="E144" t="s">
         <v>537</v>
-      </c>
-      <c r="E144" t="s">
-        <v>538</v>
       </c>
       <c r="F144" s="14" t="b">
         <v>0</v>
@@ -6193,19 +6190,19 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B145" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C145" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D145" t="s">
+        <v>536</v>
+      </c>
+      <c r="E145" t="s">
         <v>537</v>
-      </c>
-      <c r="E145" t="s">
-        <v>538</v>
       </c>
       <c r="F145" s="14" t="b">
         <v>0</v>
@@ -6214,19 +6211,19 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B146" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C146" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D146" t="s">
+        <v>536</v>
+      </c>
+      <c r="E146" t="s">
         <v>537</v>
-      </c>
-      <c r="E146" t="s">
-        <v>538</v>
       </c>
       <c r="F146" s="14" t="b">
         <v>0</v>
@@ -6235,19 +6232,19 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B147" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C147" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D147" t="s">
+        <v>530</v>
+      </c>
+      <c r="E147" t="s">
         <v>531</v>
-      </c>
-      <c r="E147" t="s">
-        <v>532</v>
       </c>
       <c r="F147" s="14" t="b">
         <v>1</v>
@@ -6256,19 +6253,19 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B148" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C148" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D148" t="s">
+        <v>536</v>
+      </c>
+      <c r="E148" t="s">
         <v>537</v>
-      </c>
-      <c r="E148" t="s">
-        <v>538</v>
       </c>
       <c r="F148" s="14" t="b">
         <v>0</v>
@@ -6277,19 +6274,19 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B149" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C149" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="D149" t="s">
+        <v>536</v>
+      </c>
+      <c r="E149" t="s">
         <v>537</v>
-      </c>
-      <c r="E149" t="s">
-        <v>538</v>
       </c>
       <c r="F149" s="14" t="b">
         <v>0</v>
@@ -6298,19 +6295,19 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B150" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C150" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D150" t="s">
+        <v>536</v>
+      </c>
+      <c r="E150" t="s">
         <v>537</v>
-      </c>
-      <c r="E150" t="s">
-        <v>538</v>
       </c>
       <c r="F150" s="14" t="b">
         <v>0</v>
@@ -6319,19 +6316,19 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B151" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C151" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D151" t="s">
+        <v>536</v>
+      </c>
+      <c r="E151" t="s">
         <v>537</v>
-      </c>
-      <c r="E151" t="s">
-        <v>538</v>
       </c>
       <c r="F151" s="14" t="b">
         <v>0</v>
@@ -6340,19 +6337,19 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B152" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C152" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D152" t="s">
+        <v>536</v>
+      </c>
+      <c r="E152" t="s">
         <v>537</v>
-      </c>
-      <c r="E152" t="s">
-        <v>538</v>
       </c>
       <c r="F152" s="14" t="b">
         <v>0</v>
@@ -6360,19 +6357,19 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B153" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C153" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D153" t="s">
+        <v>536</v>
+      </c>
+      <c r="E153" t="s">
         <v>537</v>
-      </c>
-      <c r="E153" t="s">
-        <v>538</v>
       </c>
       <c r="F153" s="14" t="b">
         <v>0</v>
@@ -6380,19 +6377,19 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B154" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C154" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D154" t="s">
+        <v>536</v>
+      </c>
+      <c r="E154" t="s">
         <v>537</v>
-      </c>
-      <c r="E154" t="s">
-        <v>538</v>
       </c>
       <c r="F154" s="14" t="b">
         <v>0</v>
@@ -6400,7 +6397,7 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155" s="11" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="F155" s="14" t="b">
         <v>0</v>
@@ -6408,13 +6405,13 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="B156" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="C156" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="F156" s="14" t="b">
         <v>1</v>
@@ -6422,13 +6419,13 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="B157" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="C157" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="F157" s="14" t="b">
         <v>1</v>
@@ -6436,13 +6433,13 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="B158" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C158" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="F158" s="14" t="b">
         <v>1</v>
@@ -6450,13 +6447,13 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B159" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="C159" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="F159" s="14" t="b">
         <v>1</v>
@@ -6464,13 +6461,13 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="B160" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="C160" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="F160" s="14" t="b">
         <v>1</v>
@@ -6478,13 +6475,13 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="B161" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C161" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="F161" s="14" t="b">
         <v>1</v>
@@ -6492,13 +6489,13 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="B162" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="C162" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="F162" s="14" t="b">
         <v>1</v>
@@ -6506,13 +6503,13 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="B163" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="C163" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="F163" s="14" t="b">
         <v>1</v>
@@ -6520,13 +6517,13 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="B164" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="C164" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="F164" s="14" t="b">
         <v>1</v>
@@ -6534,13 +6531,13 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="B165" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C165" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="F165" s="14" t="b">
         <v>1</v>
@@ -6548,13 +6545,13 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="B166" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="C166" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="F166" s="14" t="b">
         <v>1</v>
@@ -6562,13 +6559,13 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="B167" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="C167" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="F167" s="14" t="b">
         <v>1</v>
@@ -6576,13 +6573,13 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="B168" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="C168" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="F168" s="14" t="b">
         <v>1</v>
@@ -6623,7 +6620,7 @@
         <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="16" x14ac:dyDescent="0.2">
@@ -6636,10 +6633,10 @@
     </row>
     <row r="4" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="16" x14ac:dyDescent="0.2">
@@ -6671,7 +6668,7 @@
         <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="16" x14ac:dyDescent="0.2">
@@ -6679,7 +6676,7 @@
         <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="32" x14ac:dyDescent="0.2">
@@ -6719,7 +6716,7 @@
         <v>3</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="16" x14ac:dyDescent="0.2">
@@ -6727,7 +6724,7 @@
         <v>4</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="16" x14ac:dyDescent="0.2">
@@ -6791,7 +6788,7 @@
         <v>13</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="16" x14ac:dyDescent="0.2">
@@ -6799,7 +6796,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="16" x14ac:dyDescent="0.2">
@@ -6807,7 +6804,7 @@
         <v>46</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="16" x14ac:dyDescent="0.2">
@@ -6839,7 +6836,7 @@
         <v>43</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="32" x14ac:dyDescent="0.2">
@@ -6927,7 +6924,7 @@
         <v>136</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="16" x14ac:dyDescent="0.2">
@@ -6943,7 +6940,7 @@
         <v>19</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="16" x14ac:dyDescent="0.2">
@@ -6956,10 +6953,10 @@
     </row>
     <row r="44" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="16" x14ac:dyDescent="0.2">
@@ -7060,10 +7057,10 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
@@ -7105,7 +7102,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>49</v>
@@ -7140,7 +7137,7 @@
         <v>197</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -7228,7 +7225,7 @@
         <v>22</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -7241,10 +7238,10 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -7300,7 +7297,7 @@
         <v>178</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
@@ -7364,7 +7361,7 @@
         <v>179</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="16" x14ac:dyDescent="0.2">
@@ -7372,7 +7369,7 @@
         <v>189</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
@@ -7660,7 +7657,7 @@
         <v>19</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
@@ -7769,7 +7766,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
-        <v>224</v>
+        <v>275</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>165</v>
@@ -7809,10 +7806,10 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="91" spans="1:2" ht="16" x14ac:dyDescent="0.2">
@@ -7849,7 +7846,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>49</v>
@@ -7857,31 +7854,31 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B5" t="s">
         <v>185</v>
@@ -7889,7 +7886,7 @@
     </row>
     <row r="6" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>87</v>
@@ -7897,34 +7894,34 @@
     </row>
     <row r="7" spans="1:2" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>250</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
